--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{82CF9703-FF2F-4B4B-B733-F476A5C42209}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,19 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="479">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +713,783 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2167,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +3701,406 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77C53768-B540-4BE2-A6BE-446C49AAEF08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,20 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="868" uniqueCount="499">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +714,843 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2228,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +3762,508 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74323654-2238-4778-A472-4D9EF60D66DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="24" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,21 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="890" uniqueCount="519">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +715,903 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2289,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +3823,610 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4DD863F-8D79-4546-BD3F-0710069A498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="25" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,22 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="工作表1" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="912" uniqueCount="539">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +716,963 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2350,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +3884,712 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2F0B6725-4162-4FFB-902E-032A7452AE98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="26" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,23 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="559">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +717,1023 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2411,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +3945,814 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29227"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FDA91F7-C8EE-4852-87E6-A2056E19D684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="21" activeTab="27" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,24 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="579">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +718,1083 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2472,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4006,916 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29301"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8737A0F5-8DBB-4D1E-A64B-B373F722F906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="27" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,25 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
+    <sheet name="寵物日常照護小技巧" sheetId="29" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="599">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +719,1143 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
+  </si>
+  <si>
+    <t>多久要幫寵物梳毛？</t>
+  </si>
+  <si>
+    <t>短毛犬貓可每週 2–3 次，長毛品種則最好每天梳理。梳毛能減少掉毛、避免毛球或毛打結，並促進血液循環。建議使用適合毛長的梳子，例如針梳、排梳或脫毛梳。</t>
+  </si>
+  <si>
+    <t>幫寵物洗澡的頻率應該多久一次？</t>
+  </si>
+  <si>
+    <t>狗狗一般建議每 3–4 週洗一次，長毛或有皮膚問題的狗可能需要更頻繁；貓咪通常不需要定期洗澡，除非特別髒或有皮膚病。洗澡時應使用專用寵物沐浴乳，避免用人類洗髮精。</t>
+  </si>
+  <si>
+    <t>指甲要多久修剪一次？</t>
+  </si>
+  <si>
+    <t>平均每 3–4 週修剪一次，觀察指甲是否過長以致走路時會發出「喀喀」聲或卡到地板。修剪時要避開血線（粉紅色區域），若不小心剪到出血，可用止血粉或玉米粉止血。</t>
+  </si>
+  <si>
+    <t>耳朵需要清潔嗎？</t>
+  </si>
+  <si>
+    <t>需要。建議每 2–4 週檢查一次耳朵，若有耳垢或異味，可用專用耳液滴入後輕柔按摩耳根，再用棉球擦拭外耳。不要用棉花棒深入耳道，以免推擠耳垢或傷害耳膜。</t>
+  </si>
+  <si>
+    <t>寵物的牙齒要怎麼保養？</t>
+  </si>
+  <si>
+    <t>最有效的方法是刷牙，建議每週至少 2–3 次，使用寵物專用牙刷與牙膏。可搭配潔牙零食或潔牙玩具減少牙垢。定期獸醫洗牙能有效預防牙周病與口臭。</t>
+  </si>
+  <si>
+    <t>寵物的眼睛需要特別照護嗎？</t>
+  </si>
+  <si>
+    <t>應定期檢查是否有分泌物或紅腫。輕微分泌物可用溫水或無刺激的眼部清潔液擦拭。淚痕可用專用濕紙巾清理。若出現大量分泌物或持續紅腫，應盡快就醫。</t>
+  </si>
+  <si>
+    <t>如何保持寵物的腳掌清潔？</t>
+  </si>
+  <si>
+    <t>外出回家後，應用濕紙巾或溫水擦拭腳掌，保持乾淨，避免泥土與細菌殘留。若腳毛過長，可修剪腳墊周圍毛髮以減少打滑與細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物的床墊多久要清洗一次？</t>
+  </si>
+  <si>
+    <t>建議至少每 1–2 週清洗一次，使用中性洗劑或專用清潔劑，並徹底晾乾避免黴菌滋生。若寵物有皮膚病，建議更頻繁更換與消毒。</t>
+  </si>
+  <si>
+    <t>怎麼正確清潔寵物的用品？</t>
+  </si>
+  <si>
+    <t>食盆和水碗應每天清洗，玩具則依材質分別清潔（布製可機洗、橡膠製可溫水清洗）。建議使用中性清潔劑或寵物專用產品，避免殘留化學物質。</t>
+  </si>
+  <si>
+    <t>日常照護有哪些小秘訣？</t>
+  </si>
+  <si>
+    <t>建立固定的清潔習慣，例如「每天梳毛＋清理水碗、每週修剪指甲或檢查耳朵、每月洗澡或全面清潔用品」。透過日常小動作，不僅能保持寵物健康，也能增進飼主與寵物的互動關係。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2533,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4067,1018 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD183352-C60D-40A4-8FC2-88A7FCADDB84}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="73.75" customWidth="1"/>
+    <col min="2" max="2" width="104.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{07D24293-6107-4218-B0B7-D61B9A1D88DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="28" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,26 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
+    <sheet name="寵物日常照護小技巧" sheetId="29" r:id="rId29"/>
+    <sheet name="寵物飼養常見迷思破解" sheetId="30" r:id="rId30"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="619">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +720,1203 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
+  </si>
+  <si>
+    <t>多久要幫寵物梳毛？</t>
+  </si>
+  <si>
+    <t>短毛犬貓可每週 2–3 次，長毛品種則最好每天梳理。梳毛能減少掉毛、避免毛球或毛打結，並促進血液循環。建議使用適合毛長的梳子，例如針梳、排梳或脫毛梳。</t>
+  </si>
+  <si>
+    <t>幫寵物洗澡的頻率應該多久一次？</t>
+  </si>
+  <si>
+    <t>狗狗一般建議每 3–4 週洗一次，長毛或有皮膚問題的狗可能需要更頻繁；貓咪通常不需要定期洗澡，除非特別髒或有皮膚病。洗澡時應使用專用寵物沐浴乳，避免用人類洗髮精。</t>
+  </si>
+  <si>
+    <t>指甲要多久修剪一次？</t>
+  </si>
+  <si>
+    <t>平均每 3–4 週修剪一次，觀察指甲是否過長以致走路時會發出「喀喀」聲或卡到地板。修剪時要避開血線（粉紅色區域），若不小心剪到出血，可用止血粉或玉米粉止血。</t>
+  </si>
+  <si>
+    <t>耳朵需要清潔嗎？</t>
+  </si>
+  <si>
+    <t>需要。建議每 2–4 週檢查一次耳朵，若有耳垢或異味，可用專用耳液滴入後輕柔按摩耳根，再用棉球擦拭外耳。不要用棉花棒深入耳道，以免推擠耳垢或傷害耳膜。</t>
+  </si>
+  <si>
+    <t>寵物的牙齒要怎麼保養？</t>
+  </si>
+  <si>
+    <t>最有效的方法是刷牙，建議每週至少 2–3 次，使用寵物專用牙刷與牙膏。可搭配潔牙零食或潔牙玩具減少牙垢。定期獸醫洗牙能有效預防牙周病與口臭。</t>
+  </si>
+  <si>
+    <t>寵物的眼睛需要特別照護嗎？</t>
+  </si>
+  <si>
+    <t>應定期檢查是否有分泌物或紅腫。輕微分泌物可用溫水或無刺激的眼部清潔液擦拭。淚痕可用專用濕紙巾清理。若出現大量分泌物或持續紅腫，應盡快就醫。</t>
+  </si>
+  <si>
+    <t>如何保持寵物的腳掌清潔？</t>
+  </si>
+  <si>
+    <t>外出回家後，應用濕紙巾或溫水擦拭腳掌，保持乾淨，避免泥土與細菌殘留。若腳毛過長，可修剪腳墊周圍毛髮以減少打滑與細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物的床墊多久要清洗一次？</t>
+  </si>
+  <si>
+    <t>建議至少每 1–2 週清洗一次，使用中性洗劑或專用清潔劑，並徹底晾乾避免黴菌滋生。若寵物有皮膚病，建議更頻繁更換與消毒。</t>
+  </si>
+  <si>
+    <t>怎麼正確清潔寵物的用品？</t>
+  </si>
+  <si>
+    <t>食盆和水碗應每天清洗，玩具則依材質分別清潔（布製可機洗、橡膠製可溫水清洗）。建議使用中性清潔劑或寵物專用產品，避免殘留化學物質。</t>
+  </si>
+  <si>
+    <t>日常照護有哪些小秘訣？</t>
+  </si>
+  <si>
+    <t>建立固定的清潔習慣，例如「每天梳毛＋清理水碗、每週修剪指甲或檢查耳朵、每月洗澡或全面清潔用品」。透過日常小動作，不僅能保持寵物健康，也能增進飼主與寵物的互動關係。</t>
+  </si>
+  <si>
+    <t>貓咪都會喝牛奶嗎？</t>
+  </si>
+  <si>
+    <t>這是迷思。許多成年貓咪缺乏乳糖酶，喝牛奶會造成腹瀉與腸胃不適。若要補充，可以選擇市售專為貓咪設計的低乳糖或無乳糖寵物奶粉。</t>
+  </si>
+  <si>
+    <t>狗狗吃大蒜能驅蟲嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。大蒜對狗狗（以及貓咪）有毒，會破壞紅血球造成貧血。驅蟲應使用獸醫推薦的專用藥物，而不是人類的食材或偏方。</t>
+  </si>
+  <si>
+    <t>貓咪摔下來總是能四腳著地嗎？</t>
+  </si>
+  <si>
+    <t>雖然貓咪有「翻正反射」，通常能在空中扭轉身體，但並非每次都能完美落地。若高度過低或過高，都可能造成骨折或內臟傷害，因此家中陽台與窗戶必須加裝防護網。</t>
+  </si>
+  <si>
+    <t>狗狗流鼻子濕就是健康的嗎？</t>
+  </si>
+  <si>
+    <t>鼻子濕潤不一定代表健康，乾燥也不一定表示生病。狗狗健康與否應觀察精神、食慾、排泄與體溫，而不是僅靠鼻子的濕潤程度來判斷。</t>
+  </si>
+  <si>
+    <t>貓咪懷孕一定要生小貓嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。很多飼主以為懷孕後貓咪必須繁殖，但事實上貓咪可以透過結紮避免懷孕，既能降低流浪貓數量，也能減少子宮蓄膿與乳腺腫瘤的風險。</t>
+  </si>
+  <si>
+    <t>小型犬不需要運動嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。雖然小型犬活動量較低，但仍需要每日散步與遊戲來維持心理與身體健康。缺乏運動會導致肥胖與行為問題。</t>
+  </si>
+  <si>
+    <t>寵物吃骨頭對牙齒有好處嗎？</t>
+  </si>
+  <si>
+    <t>部分骨頭（特別是熟骨頭）容易碎裂，會刮傷口腔、刺穿腸胃，甚至造成腸阻塞。若要幫助清潔牙齒，應選擇專業潔牙骨或潔牙玩具，而非隨意餵食骨頭。</t>
+  </si>
+  <si>
+    <t>狗狗舔傷口能幫助傷口癒合嗎？</t>
+  </si>
+  <si>
+    <t>雖然狗狗唾液含有少量抗菌物質，但過度舔舐反而會導致感染或延遲癒合。若寵物受傷，應清潔傷口並包紮，必要時戴上伊莉莎白頭套避免舔咬。</t>
+  </si>
+  <si>
+    <t>貓咪養在家裡就不需要打疫苗嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。即使是室內貓，也可能透過人類衣物鞋子帶入病菌，或在緊急外出時暴露於風險環境。疫苗能預防致命疾病（如貓瘟），因此即使是室內貓也需要定期接種。</t>
+  </si>
+  <si>
+    <t>寵物年紀大了就不用看醫生了嗎？</t>
+  </si>
+  <si>
+    <t>完全錯誤。老年寵物更需要定期健康檢查，因為腎臟病、心臟病與腫瘤在早期常沒有明顯症狀。透過半年一次的檢查能提早發現並治療，延長壽命與生活品質。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2594,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4128,1018 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD183352-C60D-40A4-8FC2-88A7FCADDB84}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="73.75" customWidth="1"/>
+    <col min="2" max="2" width="104.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -1685,6 +5301,108 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D21220D-A8CB-405D-A443-177471D54332}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.25" customWidth="1"/>
+    <col min="2" max="2" width="111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532B40C6-DF30-4B29-B9D0-4F29D5AC34C2}">
   <dimension ref="A1:D10"/>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29303"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC51A1FA-70E2-41A7-AF1F-78CBA02D92CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="28" activeTab="30" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,27 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
+    <sheet name="寵物日常照護小技巧" sheetId="29" r:id="rId29"/>
+    <sheet name="寵物飼養常見迷思破解" sheetId="30" r:id="rId30"/>
+    <sheet name="寵物旅行與外出安全" sheetId="31" r:id="rId31"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1022" uniqueCount="639">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +721,1263 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
+  </si>
+  <si>
+    <t>多久要幫寵物梳毛？</t>
+  </si>
+  <si>
+    <t>短毛犬貓可每週 2–3 次，長毛品種則最好每天梳理。梳毛能減少掉毛、避免毛球或毛打結，並促進血液循環。建議使用適合毛長的梳子，例如針梳、排梳或脫毛梳。</t>
+  </si>
+  <si>
+    <t>幫寵物洗澡的頻率應該多久一次？</t>
+  </si>
+  <si>
+    <t>狗狗一般建議每 3–4 週洗一次，長毛或有皮膚問題的狗可能需要更頻繁；貓咪通常不需要定期洗澡，除非特別髒或有皮膚病。洗澡時應使用專用寵物沐浴乳，避免用人類洗髮精。</t>
+  </si>
+  <si>
+    <t>指甲要多久修剪一次？</t>
+  </si>
+  <si>
+    <t>平均每 3–4 週修剪一次，觀察指甲是否過長以致走路時會發出「喀喀」聲或卡到地板。修剪時要避開血線（粉紅色區域），若不小心剪到出血，可用止血粉或玉米粉止血。</t>
+  </si>
+  <si>
+    <t>耳朵需要清潔嗎？</t>
+  </si>
+  <si>
+    <t>需要。建議每 2–4 週檢查一次耳朵，若有耳垢或異味，可用專用耳液滴入後輕柔按摩耳根，再用棉球擦拭外耳。不要用棉花棒深入耳道，以免推擠耳垢或傷害耳膜。</t>
+  </si>
+  <si>
+    <t>寵物的牙齒要怎麼保養？</t>
+  </si>
+  <si>
+    <t>最有效的方法是刷牙，建議每週至少 2–3 次，使用寵物專用牙刷與牙膏。可搭配潔牙零食或潔牙玩具減少牙垢。定期獸醫洗牙能有效預防牙周病與口臭。</t>
+  </si>
+  <si>
+    <t>寵物的眼睛需要特別照護嗎？</t>
+  </si>
+  <si>
+    <t>應定期檢查是否有分泌物或紅腫。輕微分泌物可用溫水或無刺激的眼部清潔液擦拭。淚痕可用專用濕紙巾清理。若出現大量分泌物或持續紅腫，應盡快就醫。</t>
+  </si>
+  <si>
+    <t>如何保持寵物的腳掌清潔？</t>
+  </si>
+  <si>
+    <t>外出回家後，應用濕紙巾或溫水擦拭腳掌，保持乾淨，避免泥土與細菌殘留。若腳毛過長，可修剪腳墊周圍毛髮以減少打滑與細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物的床墊多久要清洗一次？</t>
+  </si>
+  <si>
+    <t>建議至少每 1–2 週清洗一次，使用中性洗劑或專用清潔劑，並徹底晾乾避免黴菌滋生。若寵物有皮膚病，建議更頻繁更換與消毒。</t>
+  </si>
+  <si>
+    <t>怎麼正確清潔寵物的用品？</t>
+  </si>
+  <si>
+    <t>食盆和水碗應每天清洗，玩具則依材質分別清潔（布製可機洗、橡膠製可溫水清洗）。建議使用中性清潔劑或寵物專用產品，避免殘留化學物質。</t>
+  </si>
+  <si>
+    <t>日常照護有哪些小秘訣？</t>
+  </si>
+  <si>
+    <t>建立固定的清潔習慣，例如「每天梳毛＋清理水碗、每週修剪指甲或檢查耳朵、每月洗澡或全面清潔用品」。透過日常小動作，不僅能保持寵物健康，也能增進飼主與寵物的互動關係。</t>
+  </si>
+  <si>
+    <t>貓咪都會喝牛奶嗎？</t>
+  </si>
+  <si>
+    <t>這是迷思。許多成年貓咪缺乏乳糖酶，喝牛奶會造成腹瀉與腸胃不適。若要補充，可以選擇市售專為貓咪設計的低乳糖或無乳糖寵物奶粉。</t>
+  </si>
+  <si>
+    <t>狗狗吃大蒜能驅蟲嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。大蒜對狗狗（以及貓咪）有毒，會破壞紅血球造成貧血。驅蟲應使用獸醫推薦的專用藥物，而不是人類的食材或偏方。</t>
+  </si>
+  <si>
+    <t>貓咪摔下來總是能四腳著地嗎？</t>
+  </si>
+  <si>
+    <t>雖然貓咪有「翻正反射」，通常能在空中扭轉身體，但並非每次都能完美落地。若高度過低或過高，都可能造成骨折或內臟傷害，因此家中陽台與窗戶必須加裝防護網。</t>
+  </si>
+  <si>
+    <t>狗狗流鼻子濕就是健康的嗎？</t>
+  </si>
+  <si>
+    <t>鼻子濕潤不一定代表健康，乾燥也不一定表示生病。狗狗健康與否應觀察精神、食慾、排泄與體溫，而不是僅靠鼻子的濕潤程度來判斷。</t>
+  </si>
+  <si>
+    <t>貓咪懷孕一定要生小貓嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。很多飼主以為懷孕後貓咪必須繁殖，但事實上貓咪可以透過結紮避免懷孕，既能降低流浪貓數量，也能減少子宮蓄膿與乳腺腫瘤的風險。</t>
+  </si>
+  <si>
+    <t>小型犬不需要運動嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。雖然小型犬活動量較低，但仍需要每日散步與遊戲來維持心理與身體健康。缺乏運動會導致肥胖與行為問題。</t>
+  </si>
+  <si>
+    <t>寵物吃骨頭對牙齒有好處嗎？</t>
+  </si>
+  <si>
+    <t>部分骨頭（特別是熟骨頭）容易碎裂，會刮傷口腔、刺穿腸胃，甚至造成腸阻塞。若要幫助清潔牙齒，應選擇專業潔牙骨或潔牙玩具，而非隨意餵食骨頭。</t>
+  </si>
+  <si>
+    <t>狗狗舔傷口能幫助傷口癒合嗎？</t>
+  </si>
+  <si>
+    <t>雖然狗狗唾液含有少量抗菌物質，但過度舔舐反而會導致感染或延遲癒合。若寵物受傷，應清潔傷口並包紮，必要時戴上伊莉莎白頭套避免舔咬。</t>
+  </si>
+  <si>
+    <t>貓咪養在家裡就不需要打疫苗嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。即使是室內貓，也可能透過人類衣物鞋子帶入病菌，或在緊急外出時暴露於風險環境。疫苗能預防致命疾病（如貓瘟），因此即使是室內貓也需要定期接種。</t>
+  </si>
+  <si>
+    <t>寵物年紀大了就不用看醫生了嗎？</t>
+  </si>
+  <si>
+    <t>完全錯誤。老年寵物更需要定期健康檢查，因為腎臟病、心臟病與腫瘤在早期常沒有明顯症狀。透過半年一次的檢查能提早發現並治療，延長壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>外出旅行前要先做哪些準備？</t>
+  </si>
+  <si>
+    <t>應先確認寵物已完成疫苗與驅蟲，攜帶健康證明、醫療記錄與常用藥物。準備運輸籠、牽繩、食物、水與便用品，並在出發前讓寵物適應運輸工具，降低不安。</t>
+  </si>
+  <si>
+    <t>如何選擇安全的運輸籠？</t>
+  </si>
+  <si>
+    <t>運輸籠應堅固耐用、透氣良好，大小需讓寵物能站立、轉身與躺下。車用或飛機用運輸籠應符合 IATA 標準，門鎖牢固，內部可放置吸水墊與熟悉的毯子，增加安全感。</t>
+  </si>
+  <si>
+    <t>帶寵物搭車時要注意什麼？</t>
+  </si>
+  <si>
+    <t>切勿讓寵物自由在車內走動，避免干擾駕駛或發生意外。應使用安全帶專用胸背帶或固定的運輸籠，並保持車內通風，避免中暑。長途行駛要定時休息，讓寵物喝水與排泄。</t>
+  </si>
+  <si>
+    <t>散步時有哪些潛在危險？</t>
+  </si>
+  <si>
+    <t>常見危險包括車輛、噪音、陌生動物或有毒植物。飼主應全程使用牽繩，避免讓寵物隨意亂跑；在不熟悉的區域散步時，建議避開草叢與垃圾區，以防誤食異物或被寄生蟲叮咬。</t>
+  </si>
+  <si>
+    <t>帶寵物去公園或寵物友善場所要注意什麼？</t>
+  </si>
+  <si>
+    <t>要確認是否有寵物活動區，並遵守當地規範。應攜帶拾便袋，隨時清理排泄物。與其他寵物互動時，要觀察牠們的肢體語言，避免衝突。若寵物有攻擊傾向，應戴上口罩或避免進入人群密集區。</t>
+  </si>
+  <si>
+    <t>寵物在外住宿時怎麼確保安全？</t>
+  </si>
+  <si>
+    <t>進入住處後，先檢查房間是否有危險物品（如電線、清潔劑、窗戶縫隙），並為寵物設置專屬休息區。可攜帶牠熟悉的毯子或玩具，降低焦慮。若需單獨留在房間，最好使用運輸籠或寵物圍欄確保安全。</t>
+  </si>
+  <si>
+    <t>寵物在外出時走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>應立即尋找並呼喊牠的名字，同時聯絡當地的動物醫院、收容所與警察。若寵物有晶片或名牌，能大幅增加找回機率。平時可在項圈上附上主人的電話號碼，並考慮使用 GPS 定位項圈。</t>
+  </si>
+  <si>
+    <t>外出時如何避免寵物中暑？</t>
+  </si>
+  <si>
+    <t>應避免在正午高溫時段散步，選擇早晨或傍晚外出。攜帶水瓶與便攜水碗，讓寵物隨時補水；停留在陰涼處休息，避免在高溫柏油路上行走，以免燙傷腳墊。</t>
+  </si>
+  <si>
+    <t>搭飛機時如何減輕寵物的壓力？</t>
+  </si>
+  <si>
+    <t>出發前先讓寵物熟悉航空箱，放置熟悉的毯子與玩具。起飛前避免餵食大量食物，僅給少量水。若寵物極度緊張，可諮詢獸醫使用天然鎮定劑或藥物，但需在專業指導下使用。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些保險可以考慮？</t>
+  </si>
+  <si>
+    <t>市面上有寵物醫療險與旅行險，可涵蓋突發疾病、意外受傷或走失協尋等保障。若計畫長途旅行，建議提前為寵物投保，確保在外地也能獲得即時醫療與安全保障。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2655,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4189,1018 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD183352-C60D-40A4-8FC2-88A7FCADDB84}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="73.75" customWidth="1"/>
+    <col min="2" max="2" width="104.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -1685,6 +5362,210 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D21220D-A8CB-405D-A443-177471D54332}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.25" customWidth="1"/>
+    <col min="2" max="2" width="111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBC5497-E548-47C1-92AE-6F40EA344E03}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="70.875" customWidth="1"/>
+    <col min="2" max="2" width="103.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>629</v>
+      </c>
+      <c r="B7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B8" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>633</v>
+      </c>
+      <c r="B9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>635</v>
+      </c>
+      <c r="B10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532B40C6-DF30-4B29-B9D0-4F29D5AC34C2}">
   <dimension ref="A1:D10"/>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{34916415-641E-414C-91FD-0E8E492D9FDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="30" activeTab="31" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,28 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
+    <sheet name="寵物日常照護小技巧" sheetId="29" r:id="rId29"/>
+    <sheet name="寵物飼養常見迷思破解" sheetId="30" r:id="rId30"/>
+    <sheet name="寵物旅行與外出安全" sheetId="31" r:id="rId31"/>
+    <sheet name="寵物訓練基礎入門" sheetId="32" r:id="rId32"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="659">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +722,1323 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
+  </si>
+  <si>
+    <t>多久要幫寵物梳毛？</t>
+  </si>
+  <si>
+    <t>短毛犬貓可每週 2–3 次，長毛品種則最好每天梳理。梳毛能減少掉毛、避免毛球或毛打結，並促進血液循環。建議使用適合毛長的梳子，例如針梳、排梳或脫毛梳。</t>
+  </si>
+  <si>
+    <t>幫寵物洗澡的頻率應該多久一次？</t>
+  </si>
+  <si>
+    <t>狗狗一般建議每 3–4 週洗一次，長毛或有皮膚問題的狗可能需要更頻繁；貓咪通常不需要定期洗澡，除非特別髒或有皮膚病。洗澡時應使用專用寵物沐浴乳，避免用人類洗髮精。</t>
+  </si>
+  <si>
+    <t>指甲要多久修剪一次？</t>
+  </si>
+  <si>
+    <t>平均每 3–4 週修剪一次，觀察指甲是否過長以致走路時會發出「喀喀」聲或卡到地板。修剪時要避開血線（粉紅色區域），若不小心剪到出血，可用止血粉或玉米粉止血。</t>
+  </si>
+  <si>
+    <t>耳朵需要清潔嗎？</t>
+  </si>
+  <si>
+    <t>需要。建議每 2–4 週檢查一次耳朵，若有耳垢或異味，可用專用耳液滴入後輕柔按摩耳根，再用棉球擦拭外耳。不要用棉花棒深入耳道，以免推擠耳垢或傷害耳膜。</t>
+  </si>
+  <si>
+    <t>寵物的牙齒要怎麼保養？</t>
+  </si>
+  <si>
+    <t>最有效的方法是刷牙，建議每週至少 2–3 次，使用寵物專用牙刷與牙膏。可搭配潔牙零食或潔牙玩具減少牙垢。定期獸醫洗牙能有效預防牙周病與口臭。</t>
+  </si>
+  <si>
+    <t>寵物的眼睛需要特別照護嗎？</t>
+  </si>
+  <si>
+    <t>應定期檢查是否有分泌物或紅腫。輕微分泌物可用溫水或無刺激的眼部清潔液擦拭。淚痕可用專用濕紙巾清理。若出現大量分泌物或持續紅腫，應盡快就醫。</t>
+  </si>
+  <si>
+    <t>如何保持寵物的腳掌清潔？</t>
+  </si>
+  <si>
+    <t>外出回家後，應用濕紙巾或溫水擦拭腳掌，保持乾淨，避免泥土與細菌殘留。若腳毛過長，可修剪腳墊周圍毛髮以減少打滑與細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物的床墊多久要清洗一次？</t>
+  </si>
+  <si>
+    <t>建議至少每 1–2 週清洗一次，使用中性洗劑或專用清潔劑，並徹底晾乾避免黴菌滋生。若寵物有皮膚病，建議更頻繁更換與消毒。</t>
+  </si>
+  <si>
+    <t>怎麼正確清潔寵物的用品？</t>
+  </si>
+  <si>
+    <t>食盆和水碗應每天清洗，玩具則依材質分別清潔（布製可機洗、橡膠製可溫水清洗）。建議使用中性清潔劑或寵物專用產品，避免殘留化學物質。</t>
+  </si>
+  <si>
+    <t>日常照護有哪些小秘訣？</t>
+  </si>
+  <si>
+    <t>建立固定的清潔習慣，例如「每天梳毛＋清理水碗、每週修剪指甲或檢查耳朵、每月洗澡或全面清潔用品」。透過日常小動作，不僅能保持寵物健康，也能增進飼主與寵物的互動關係。</t>
+  </si>
+  <si>
+    <t>貓咪都會喝牛奶嗎？</t>
+  </si>
+  <si>
+    <t>這是迷思。許多成年貓咪缺乏乳糖酶，喝牛奶會造成腹瀉與腸胃不適。若要補充，可以選擇市售專為貓咪設計的低乳糖或無乳糖寵物奶粉。</t>
+  </si>
+  <si>
+    <t>狗狗吃大蒜能驅蟲嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。大蒜對狗狗（以及貓咪）有毒，會破壞紅血球造成貧血。驅蟲應使用獸醫推薦的專用藥物，而不是人類的食材或偏方。</t>
+  </si>
+  <si>
+    <t>貓咪摔下來總是能四腳著地嗎？</t>
+  </si>
+  <si>
+    <t>雖然貓咪有「翻正反射」，通常能在空中扭轉身體，但並非每次都能完美落地。若高度過低或過高，都可能造成骨折或內臟傷害，因此家中陽台與窗戶必須加裝防護網。</t>
+  </si>
+  <si>
+    <t>狗狗流鼻子濕就是健康的嗎？</t>
+  </si>
+  <si>
+    <t>鼻子濕潤不一定代表健康，乾燥也不一定表示生病。狗狗健康與否應觀察精神、食慾、排泄與體溫，而不是僅靠鼻子的濕潤程度來判斷。</t>
+  </si>
+  <si>
+    <t>貓咪懷孕一定要生小貓嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。很多飼主以為懷孕後貓咪必須繁殖，但事實上貓咪可以透過結紮避免懷孕，既能降低流浪貓數量，也能減少子宮蓄膿與乳腺腫瘤的風險。</t>
+  </si>
+  <si>
+    <t>小型犬不需要運動嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。雖然小型犬活動量較低，但仍需要每日散步與遊戲來維持心理與身體健康。缺乏運動會導致肥胖與行為問題。</t>
+  </si>
+  <si>
+    <t>寵物吃骨頭對牙齒有好處嗎？</t>
+  </si>
+  <si>
+    <t>部分骨頭（特別是熟骨頭）容易碎裂，會刮傷口腔、刺穿腸胃，甚至造成腸阻塞。若要幫助清潔牙齒，應選擇專業潔牙骨或潔牙玩具，而非隨意餵食骨頭。</t>
+  </si>
+  <si>
+    <t>狗狗舔傷口能幫助傷口癒合嗎？</t>
+  </si>
+  <si>
+    <t>雖然狗狗唾液含有少量抗菌物質，但過度舔舐反而會導致感染或延遲癒合。若寵物受傷，應清潔傷口並包紮，必要時戴上伊莉莎白頭套避免舔咬。</t>
+  </si>
+  <si>
+    <t>貓咪養在家裡就不需要打疫苗嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。即使是室內貓，也可能透過人類衣物鞋子帶入病菌，或在緊急外出時暴露於風險環境。疫苗能預防致命疾病（如貓瘟），因此即使是室內貓也需要定期接種。</t>
+  </si>
+  <si>
+    <t>寵物年紀大了就不用看醫生了嗎？</t>
+  </si>
+  <si>
+    <t>完全錯誤。老年寵物更需要定期健康檢查，因為腎臟病、心臟病與腫瘤在早期常沒有明顯症狀。透過半年一次的檢查能提早發現並治療，延長壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>外出旅行前要先做哪些準備？</t>
+  </si>
+  <si>
+    <t>應先確認寵物已完成疫苗與驅蟲，攜帶健康證明、醫療記錄與常用藥物。準備運輸籠、牽繩、食物、水與便用品，並在出發前讓寵物適應運輸工具，降低不安。</t>
+  </si>
+  <si>
+    <t>如何選擇安全的運輸籠？</t>
+  </si>
+  <si>
+    <t>運輸籠應堅固耐用、透氣良好，大小需讓寵物能站立、轉身與躺下。車用或飛機用運輸籠應符合 IATA 標準，門鎖牢固，內部可放置吸水墊與熟悉的毯子，增加安全感。</t>
+  </si>
+  <si>
+    <t>帶寵物搭車時要注意什麼？</t>
+  </si>
+  <si>
+    <t>切勿讓寵物自由在車內走動，避免干擾駕駛或發生意外。應使用安全帶專用胸背帶或固定的運輸籠，並保持車內通風，避免中暑。長途行駛要定時休息，讓寵物喝水與排泄。</t>
+  </si>
+  <si>
+    <t>散步時有哪些潛在危險？</t>
+  </si>
+  <si>
+    <t>常見危險包括車輛、噪音、陌生動物或有毒植物。飼主應全程使用牽繩，避免讓寵物隨意亂跑；在不熟悉的區域散步時，建議避開草叢與垃圾區，以防誤食異物或被寄生蟲叮咬。</t>
+  </si>
+  <si>
+    <t>帶寵物去公園或寵物友善場所要注意什麼？</t>
+  </si>
+  <si>
+    <t>要確認是否有寵物活動區，並遵守當地規範。應攜帶拾便袋，隨時清理排泄物。與其他寵物互動時，要觀察牠們的肢體語言，避免衝突。若寵物有攻擊傾向，應戴上口罩或避免進入人群密集區。</t>
+  </si>
+  <si>
+    <t>寵物在外住宿時怎麼確保安全？</t>
+  </si>
+  <si>
+    <t>進入住處後，先檢查房間是否有危險物品（如電線、清潔劑、窗戶縫隙），並為寵物設置專屬休息區。可攜帶牠熟悉的毯子或玩具，降低焦慮。若需單獨留在房間，最好使用運輸籠或寵物圍欄確保安全。</t>
+  </si>
+  <si>
+    <t>寵物在外出時走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>應立即尋找並呼喊牠的名字，同時聯絡當地的動物醫院、收容所與警察。若寵物有晶片或名牌，能大幅增加找回機率。平時可在項圈上附上主人的電話號碼，並考慮使用 GPS 定位項圈。</t>
+  </si>
+  <si>
+    <t>外出時如何避免寵物中暑？</t>
+  </si>
+  <si>
+    <t>應避免在正午高溫時段散步，選擇早晨或傍晚外出。攜帶水瓶與便攜水碗，讓寵物隨時補水；停留在陰涼處休息，避免在高溫柏油路上行走，以免燙傷腳墊。</t>
+  </si>
+  <si>
+    <t>搭飛機時如何減輕寵物的壓力？</t>
+  </si>
+  <si>
+    <t>出發前先讓寵物熟悉航空箱，放置熟悉的毯子與玩具。起飛前避免餵食大量食物，僅給少量水。若寵物極度緊張，可諮詢獸醫使用天然鎮定劑或藥物，但需在專業指導下使用。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些保險可以考慮？</t>
+  </si>
+  <si>
+    <t>市面上有寵物醫療險與旅行險，可涵蓋突發疾病、意外受傷或走失協尋等保障。若計畫長途旅行，建議提前為寵物投保，確保在外地也能獲得即時醫療與安全保障。</t>
+  </si>
+  <si>
+    <t>為什麼要訓練寵物？</t>
+  </si>
+  <si>
+    <t>訓練不只是讓寵物聽話，更能增進飼主與寵物的溝通，避免危險行為（如亂跑、咬人），並提供心理刺激。良好的訓練能讓生活更有秩序，也能提升寵物的安全與幸福感。</t>
+  </si>
+  <si>
+    <t>什麼是「正向強化」訓練？</t>
+  </si>
+  <si>
+    <t>正向強化是當寵物表現正確行為時，立即給予獎勵（零食、撫摸或口頭稱讚），讓牠將行為與好結果連結，進而增加該行為的出現頻率。這是目前最科學且有效的訓練方法。</t>
+  </si>
+  <si>
+    <t>如何教狗狗「坐下」？</t>
+  </si>
+  <si>
+    <t>先拿零食在狗狗鼻子前，慢慢往上移動，當牠自然坐下時立即獎勵，並同時說出口令「坐下」。重複練習數次，狗狗就能將動作與口令建立連結。</t>
+  </si>
+  <si>
+    <t>如何教狗狗「等待」？</t>
+  </si>
+  <si>
+    <t>讓狗狗坐下後舉起手掌，清楚說「等」。若狗狗保持不動幾秒，就給獎勵。逐步延長時間與距離，並在結束時加上「好」或「來」解除口令。這能幫助建立自控力。</t>
+  </si>
+  <si>
+    <t>如何訓練狗狗定點如廁？</t>
+  </si>
+  <si>
+    <t>應在固定時間帶狗狗到指定位置排泄，並在完成後立即獎勵。若在錯誤地點排泄，要立即清理並去除氣味，避免牠再次在同處如廁。幼犬需更頻繁帶去，建立習慣後就能逐漸穩定。</t>
+  </si>
+  <si>
+    <t>貓咪能被訓練嗎？</t>
+  </si>
+  <si>
+    <t>能。雖然貓咪不像狗狗那樣追求主人的指令，但透過零食與玩具獎勵，也能學會簡單指令（如「過來」、「高五」）。關鍵是使用短時間、多次練習，避免強迫。</t>
+  </si>
+  <si>
+    <t>如何讓寵物學會「過來」？</t>
+  </si>
+  <si>
+    <t>在家中短距離開始，蹲下呼喚名字並說「過來」，當牠靠近就立即給獎勵。可逐漸增加距離與干擾環境，最終達到在戶外也能可靠回應，這是確保安全的重要訓練。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應牽繩？</t>
+  </si>
+  <si>
+    <t>應先在家中或安靜環境讓牠熟悉胸背帶與牽繩，當牠冷靜走在旁邊時給予獎勵。若拉扯，應立刻停下不前進，等牠鬆開後再繼續走，讓牠明白拉扯無法達到目的。</t>
+  </si>
+  <si>
+    <t>寵物咬東西怎麼糾正？</t>
+  </si>
+  <si>
+    <t>不要責罵，而是提供正確的替代品（咬咬玩具）。若咬到不該咬的東西，應立即制止並引導到玩具上，當牠選擇正確物品時給獎勵，逐步建立好習慣。</t>
+  </si>
+  <si>
+    <t>訓練過程中常見的錯誤有哪些？</t>
+  </si>
+  <si>
+    <t>常見錯誤包括訓練時間過長導致寵物失去專注、口令不一致（家人用不同詞）、責罵或體罰、沒有即時獎勵。訓練應簡短（5–10 分鐘）、一致且愉快，讓寵物覺得學習是快樂的事。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2716,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4250,1018 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD183352-C60D-40A4-8FC2-88A7FCADDB84}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="73.75" customWidth="1"/>
+    <col min="2" max="2" width="104.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -1685,6 +5423,312 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D21220D-A8CB-405D-A443-177471D54332}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.25" customWidth="1"/>
+    <col min="2" max="2" width="111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBC5497-E548-47C1-92AE-6F40EA344E03}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="70.875" customWidth="1"/>
+    <col min="2" max="2" width="103.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>629</v>
+      </c>
+      <c r="B7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B8" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>633</v>
+      </c>
+      <c r="B9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>635</v>
+      </c>
+      <c r="B10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{646C2F24-950B-4A5B-BF35-AA4D88D15B44}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="62.875" customWidth="1"/>
+    <col min="2" max="2" width="109.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B6" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>649</v>
+      </c>
+      <c r="B7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>653</v>
+      </c>
+      <c r="B9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532B40C6-DF30-4B29-B9D0-4F29D5AC34C2}">
   <dimension ref="A1:D10"/>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EECAA1C4-0693-4B12-8F8A-453CEAE235AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D74EE07-35D4-4BD0-8F58-BE89CB748E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="6" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="31" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,29 @@
     <sheet name="旅遊與外出" sheetId="8" r:id="rId8"/>
     <sheet name="老年寵物照護" sheetId="9" r:id="rId9"/>
     <sheet name="特殊情況應對（走失、中毒、交配等）" sheetId="10" r:id="rId10"/>
+    <sheet name="進階飼養知識" sheetId="11" r:id="rId11"/>
+    <sheet name="繁殖與成長知識" sheetId="12" r:id="rId12"/>
+    <sheet name=" 寵物心理與情緒" sheetId="13" r:id="rId13"/>
+    <sheet name=" 醫療與保健補充" sheetId="14" r:id="rId14"/>
+    <sheet name="社群與紀錄" sheetId="15" r:id="rId15"/>
+    <sheet name="寵物居家急救與緊急應變" sheetId="16" r:id="rId16"/>
+    <sheet name="寵物日常行為問題與改善方法" sheetId="17" r:id="rId17"/>
+    <sheet name="帶寵物出門與旅行注意事項" sheetId="18" r:id="rId18"/>
+    <sheet name="寵物健康檢查與保健" sheetId="19" r:id="rId19"/>
+    <sheet name="寵物飲食與營養管理" sheetId="20" r:id="rId20"/>
+    <sheet name="寵物心理與情緒照護" sheetId="21" r:id="rId21"/>
+    <sheet name="寵物居家安全與防護" sheetId="22" r:id="rId22"/>
+    <sheet name="寵物常見疾病與預防" sheetId="23" r:id="rId23"/>
+    <sheet name="寵物運動與遊戲" sheetId="24" r:id="rId24"/>
+    <sheet name="寵物常見行為矯正" sheetId="25" r:id="rId25"/>
+    <sheet name="寵物與小孩的相處" sheetId="26" r:id="rId26"/>
+    <sheet name="寵物居家清潔與衛生" sheetId="27" r:id="rId27"/>
+    <sheet name="寵物緊急狀況處理" sheetId="28" r:id="rId28"/>
+    <sheet name="寵物日常照護小技巧" sheetId="29" r:id="rId29"/>
+    <sheet name="寵物飼養常見迷思破解" sheetId="30" r:id="rId30"/>
+    <sheet name="寵物旅行與外出安全" sheetId="31" r:id="rId31"/>
+    <sheet name="寵物訓練基礎入門" sheetId="32" r:id="rId32"/>
+    <sheet name="寵物營養補充與保健品" sheetId="33" r:id="rId33"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -40,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="679">
   <si>
     <t>Q1</t>
   </si>
@@ -700,6 +723,1383 @@
   </si>
   <si>
     <t>長期承諾、愛與耐心，讓牠成為你家庭的一份子。</t>
+  </si>
+  <si>
+    <t>狗狗會認主人嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗有認知能力與記憶，能辨識主人的氣味、聲音與臉孔。</t>
+  </si>
+  <si>
+    <t>飼養第二隻狗會比較好嗎？</t>
+  </si>
+  <si>
+    <t>需視原本狗狗個性與飼主照顧能力，避免因競爭反而壓力更大。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪會磨爪？</t>
+  </si>
+  <si>
+    <t>是本能行為，為了去除老化爪殼與標記地盤。</t>
+  </si>
+  <si>
+    <t>狗狗有色盲嗎？</t>
+  </si>
+  <si>
+    <t>狗狗視覺有限，能分辨藍與黃色，但紅綠色較難辨識。</t>
+  </si>
+  <si>
+    <t>怎麼區分公母寵物？</t>
+  </si>
+  <si>
+    <t>狗貓生殖器官在幼年即可辨別，獸醫也可協助判定。</t>
+  </si>
+  <si>
+    <t>貓咪會記仇嗎？</t>
+  </si>
+  <si>
+    <t>不會「記仇」，但會記得不愉快經驗並避免再接近。</t>
+  </si>
+  <si>
+    <t>寵物需要刷毛嗎？</t>
+  </si>
+  <si>
+    <t>是。可去除死毛、促進血液循環，尤其長毛品種需天天梳理。</t>
+  </si>
+  <si>
+    <t>寵物會作夢嗎？</t>
+  </si>
+  <si>
+    <t>是。研究顯示動物在睡眠中也會有REM期，會抽動四肢或發出聲音。</t>
+  </si>
+  <si>
+    <t>如何幫寵物拍照？</t>
+  </si>
+  <si>
+    <t>用自然光、低角度拍攝並吸引注意力；可用聲音或點心誘導。</t>
+  </si>
+  <si>
+    <t>寵物會認路回家嗎？</t>
+  </si>
+  <si>
+    <t>有些狗貓有方向感，但不可靠，仍應避免走失風險。</t>
+  </si>
+  <si>
+    <t>狗狗幾歲性成熟？</t>
+  </si>
+  <si>
+    <t>一般6–12個月，依品種體型不同略有差異。</t>
+  </si>
+  <si>
+    <t>發情期持續多久？</t>
+  </si>
+  <si>
+    <t>母狗約2–3週，貓則約7天左右。</t>
+  </si>
+  <si>
+    <t>怎麼知道母狗懷孕了？</t>
+  </si>
+  <si>
+    <t>胃部變大、乳頭變色、活動力下降，建議照超音波確認。</t>
+  </si>
+  <si>
+    <t>寵物懷孕需要補充營養嗎？</t>
+  </si>
+  <si>
+    <t>是，需增加蛋白質與熱量，請獸醫建議適當配方。</t>
+  </si>
+  <si>
+    <t>狗貓一次生幾隻？</t>
+  </si>
+  <si>
+    <t>看品種大小，狗約4–10隻，貓約3–6隻。</t>
+  </si>
+  <si>
+    <t>小狗幾週可以吃副食品</t>
+  </si>
+  <si>
+    <t>約3–4週開始離乳，可吃濕軟的幼犬飼料。</t>
+  </si>
+  <si>
+    <t>貓咪會照顧小貓嗎？</t>
+  </si>
+  <si>
+    <t>會，母貓具有強烈護子本能，建議不要過度打擾。</t>
+  </si>
+  <si>
+    <t>小狗幾個月可離乳？</t>
+  </si>
+  <si>
+    <t>通常在6–8週左右完成斷奶。</t>
+  </si>
+  <si>
+    <t>要幫寵物登記出生資訊嗎？</t>
+  </si>
+  <si>
+    <t>若參加比賽或育種，血統登記需提交出生證明。</t>
+  </si>
+  <si>
+    <t>什麼是基因遺傳病？</t>
+  </si>
+  <si>
+    <t>特定品種易攜帶疾病基因，如髖關節異常、視網膜萎縮等。</t>
+  </si>
+  <si>
+    <t>寵物會吃醋嗎？</t>
+  </si>
+  <si>
+    <t>會有類似情緒，當注意力分散時會出現行為改變。</t>
+  </si>
+  <si>
+    <t>怎麼看出寵物開心？</t>
+  </si>
+  <si>
+    <t>尾巴搖擺、靠近你、主動玩耍與呼嚕聲（貓）。</t>
+  </si>
+  <si>
+    <t>寵物會憂鬱嗎？</t>
+  </si>
+  <si>
+    <t>長期孤單或改變環境會讓寵物表現冷淡、食慾下降。</t>
+  </si>
+  <si>
+    <t>如何陪伴老年寵物？</t>
+  </si>
+  <si>
+    <t>每天與牠互動、輕柔按摩與話語交流，可讓牠安心。</t>
+  </si>
+  <si>
+    <t>怎麼緩解分離焦慮？</t>
+  </si>
+  <si>
+    <t>使用陪伴玩具、建立獨處時間、逐漸延長離開時間。</t>
+  </si>
+  <si>
+    <t>寵物為什麼會亂大小便？</t>
+  </si>
+  <si>
+    <t>可能是壓力、健康問題或訓練不完全所致。</t>
+  </si>
+  <si>
+    <t>寵物會感到被忽略嗎？</t>
+  </si>
+  <si>
+    <t>會。長時間無互動可能導致情緒行為問題。</t>
+  </si>
+  <si>
+    <t>怎麼安撫害怕的狗？</t>
+  </si>
+  <si>
+    <t>低聲安撫、避免擁抱強壓、可使用抗焦慮噴劑或外套。</t>
+  </si>
+  <si>
+    <t>打雷時寵物躲起來正常嗎</t>
+  </si>
+  <si>
+    <t>是正常壓力反應，可提供安全空間讓牠藏匿。</t>
+  </si>
+  <si>
+    <t>寵物認得自己的名字嗎？</t>
+  </si>
+  <si>
+    <t>經常呼喚與獎勵能讓牠辨認並回應名字。</t>
+  </si>
+  <si>
+    <t>寵物會蛀牙嗎？</t>
+  </si>
+  <si>
+    <t>狗貓也會牙結石與牙周病，需定期潔牙。</t>
+  </si>
+  <si>
+    <t>如何幫寵物刷牙？</t>
+  </si>
+  <si>
+    <t>使用寵物牙膏與專用牙刷，一週至少2次。</t>
+  </si>
+  <si>
+    <t>寵物流口水是生病嗎？</t>
+  </si>
+  <si>
+    <t>若頻繁、黏稠，可能為口腔問題或中毒徵兆。</t>
+  </si>
+  <si>
+    <t>寵物貧血有哪些症狀？</t>
+  </si>
+  <si>
+    <t>虛弱、黏膜蒼白、食慾不佳，需抽血檢查。</t>
+  </si>
+  <si>
+    <t>可以給寵物保健食品嗎？</t>
+  </si>
+  <si>
+    <t>可以，但須選擇適合種類與依建議劑量使用。</t>
+  </si>
+  <si>
+    <t>寵物生病該看哪科？</t>
+  </si>
+  <si>
+    <t>多數為「小動物內科」，特殊科如眼科、皮膚科可進一步轉診。</t>
+  </si>
+  <si>
+    <t>疫苗打了還會得病嗎？</t>
+  </si>
+  <si>
+    <t>仍有極小機率感染，但症狀較輕，保護力仍高。</t>
+  </si>
+  <si>
+    <t>寵物需要輸血嗎？</t>
+  </si>
+  <si>
+    <t>有些重病或外傷時確實需輸血，獸醫會做交叉配對。</t>
+  </si>
+  <si>
+    <t>醫療費太貴怎麼辦？</t>
+  </si>
+  <si>
+    <t>可考慮投保寵物保險，平時定期檢查預防重症。</t>
+  </si>
+  <si>
+    <t>寵物能做復健嗎？</t>
+  </si>
+  <si>
+    <t>有。如水療、磁療、關節伸展可改善術後或老年問題。</t>
+  </si>
+  <si>
+    <t>如何幫寵物做紀錄？</t>
+  </si>
+  <si>
+    <t>可用APP記錄疫苗、醫療、體重與飲食。</t>
+  </si>
+  <si>
+    <t>寵物可以上IG/TikTok嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，許多毛孩都有自己的帳號與粉絲。</t>
+  </si>
+  <si>
+    <t>寵物寫真需要專業拍嗎？</t>
+  </si>
+  <si>
+    <t>可找寵物攝影師或使用手機搭配道具、背景拍攝。</t>
+  </si>
+  <si>
+    <t>可以幫寵物穿衣服嗎？</t>
+  </si>
+  <si>
+    <t>若天氣寒冷或皮膚保護需要，可適度穿著。</t>
+  </si>
+  <si>
+    <t>怎麼做寵物成長相簿？</t>
+  </si>
+  <si>
+    <t>每月拍攝1張，記錄從幼年到成年的變化。</t>
+  </si>
+  <si>
+    <t>有寵物專屬的社交平台嗎？</t>
+  </si>
+  <si>
+    <t>有，如Petpetgo、毛起來愛、Wag等。</t>
+  </si>
+  <si>
+    <t>怎麼辦寵物生日派對？</t>
+  </si>
+  <si>
+    <t>預約寵物友善空間、製作蛋糕、準備服飾與禮物。</t>
+  </si>
+  <si>
+    <t>可以幫寵物取綽號嗎？</t>
+  </si>
+  <si>
+    <t>當然可以，牠們會記住你給予的稱呼與語調。</t>
+  </si>
+  <si>
+    <t>寵物會喜歡照鏡子嗎？</t>
+  </si>
+  <si>
+    <t>多數不會認出自己，但有些會出現好奇或敵意。</t>
+  </si>
+  <si>
+    <t>寵物紀錄資料要備份嗎？</t>
+  </si>
+  <si>
+    <t>建議雲端備份，以防遺失重要健康與身分資料。</t>
+  </si>
+  <si>
+    <t>怎麼判斷是不是緊急？</t>
+  </si>
+  <si>
+    <t>可先檢查寵物是否意識清楚、呼吸順暢、心跳正常，並觀察牙齦顏色與毛細血管回填時間（按壓牙齦放開後應在 2 秒內恢復粉紅）。任何出現呼吸困難、持續抽搐、昏迷、大量出血、疑似中毒、高燒或體溫過低、突然無法站立等情況，都屬於緊急狀況，需立即送往動物醫院，同時在運送途中盡可能保持呼吸道暢通與體溫穩定。</t>
+  </si>
+  <si>
+    <t>寵物噎到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若寵物仍能咳嗽或發出聲音，應保持鎮定並鼓勵牠自行排出異物，不要隨意伸手進嘴巴掏取；若完全無法呼吸、發聲且牙齦變紫，表示是完全阻塞，此時需立刻進行急救，例如小型犬貓可抱起頭朝下拍背、胸腔擠壓，大型犬可採立姿或側躺進行腹部擠壓（哈姆立克法），並在每次動作後檢查口腔是否可見異物，同時盡快送醫。</t>
+  </si>
+  <si>
+    <t>怎麼對犬貓做 CPR？</t>
+  </si>
+  <si>
+    <t>當寵物沒有呼吸且摸不到脈搏時，需立刻進行 CPR。將寵物側躺，雙手置於胸腔最寬處垂直下壓，頻率為每分鐘 100–120 次，深度約為胸腔寬度的 1/3–1/2；按壓 30 次後進行 2 次人工呼吸（口對鼻吹氣，胸廓輕微抬起為宜），並持續循環直到恢復心跳或交由獸醫處理。施救過程中需避免過度吹氣導致胃脹氣，並盡可能保持按壓不中斷。</t>
+  </si>
+  <si>
+    <t>中暑有哪些徵兆與應對方法？</t>
+  </si>
+  <si>
+    <t>寵物中暑常見症狀包括喘促不止、流口水、步態不穩、嘔吐腹瀉、牙齦鮮紅或發白、虛弱甚至昏迷。發現疑似中暑時，應立即將牠移至陰涼通風處，卸下項圈和口罩，使用溫涼水（非冰水）打濕腹股溝、腋下與腳墊，並用電扇輔助降溫，當體溫降至約 39.5°C 即停止主動降溫以避免低溫過度，能吞嚥的情況下可少量飲水，並立即送醫檢查。</t>
+  </si>
+  <si>
+    <t>遇到癲癇發作怎麼辦？</t>
+  </si>
+  <si>
+    <t>發作時不要將手或物品放入口中，避免咬傷或造成更多損害，應將周圍尖銳物移開並保持環境安靜，讓寵物躺在安全的平面並在頭下墊軟布，持續觀察並計時，若發作超過 5 分鐘或短時間內重複發作，屬於危急狀況，需立即送醫；發作停止後讓牠安靜休息並保暖，並記錄過程（影片或描述）供獸醫診斷。</t>
+  </si>
+  <si>
+    <t>寵物大出血時怎麼止血？</t>
+  </si>
+  <si>
+    <t>應立即以乾淨紗布或布料直接壓迫出血處 3–5 分鐘，期間不要掀開檢查，以免影響凝血，若血液滲出應在外層加疊新的紗布持續加壓，必要時用棉墊和彈性繃帶固定並確保末端肢體不因包紮過緊而變紫或冰冷；若出血量大且來自動脈，且無法以壓迫控制，可在上方使用止血帶暫時止血，每 2–3 分鐘稍微放鬆一次，並儘快送醫。</t>
+  </si>
+  <si>
+    <t>寵物中毒時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>先將寵物移離毒源並確保牠安全，保留可能的毒物包裝、殘留物或植物樣本，記下攝入時間與大約的量，並立即聯絡獸醫；在未經獸醫指示下不要自行催吐，尤其是腐蝕性物質、昏迷或抽搐的情況下更危險。運送途中應保持安靜、避免奔跑以減少毒物吸收，並將毒物資訊完整告知獸醫以利處理。</t>
+  </si>
+  <si>
+    <t>骨折或脫臼怎麼處理？</t>
+  </si>
+  <si>
+    <t>不要自行復位，應盡量限制受傷部位的活動，可用毛巾或布條將患肢靠近身體固定，或使用硬板作為臨時夾板固定上下關節，避免進一步移動造成二次傷害；若同時有出血，先止血再固定，並在運送過程中減少顛簸，盡快送醫做 X 光檢查與治療。</t>
+  </si>
+  <si>
+    <t>燒燙傷該如何急救？</t>
+  </si>
+  <si>
+    <t>熱燙傷應立即用 15–25°C 的涼水沖洗傷口 10–15 分鐘以降溫，但不要使用冰塊；化學灼傷需大量清水沖洗至少 15 分鐘並避免觸碰傷口周邊；電灼傷要先切斷電源再接近寵物，以免自己觸電。任何燒燙傷都不要塗抹牙膏、油膏等物質，應保持傷口清潔覆蓋並立即送醫，以防感染與評估深度。</t>
+  </si>
+  <si>
+    <t>眼睛受傷時怎麼辦？</t>
+  </si>
+  <si>
+    <t>眼睛受傷時不要直接用手拔除異物，可用生理食鹽水輕柔沖洗以去除表面灰塵，避免用力過大傷到角膜；應防止寵物用爪子抓眼睛，可戴上伊莉莎白頭套保護；若眼睛流血、腫脹、渾濁或眼球外突，應用乾淨紗布輕蓋保護並立即送醫，因為眼部損傷處理時效性非常關鍵，拖延可能造成永久失明。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會一直吠叫？</t>
+  </si>
+  <si>
+    <t>持續吠叫可能是因為警戒、分離焦慮、無聊、想引起注意或對外界刺激反應。首先要找出原因，例如外面有陌生人經過、缺乏運動、或因主人才回家而興奮。改善方式包括增加每日運動量、提供玩具轉移注意力、用「安靜」口令配合獎勵訓練，以及遮蔽外部視線；若是焦慮問題，可透過逐步脫敏訓練與環境安撫來減輕。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會亂抓家具？</t>
+  </si>
+  <si>
+    <t>抓東西是貓的天性，除了磨爪外，還有標記氣味與舒展肌肉的作用。要改善，可以提供足夠的貓抓板（直立與水平型皆有），放在牠常抓的位置；當牠使用抓板時給予零食或撫摸獎勵，若抓家具時則用拍手或轉移注意力制止，同時用保護膜或雙面膠貼在家具表面減少吸引力。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡撲人怎麼辦？</t>
+  </si>
+  <si>
+    <t>撲人通常是打招呼或索取關注的行為，但可能嚇到小孩或客人。訓練時，當狗狗撲人應立即轉身忽視，等牠四腳著地並安靜下來再給予獎勵；同時教導「坐下」作為替代行為，讓牠學會用坐下來換取注意與撫摸。</t>
+  </si>
+  <si>
+    <t>貓咪半夜亂跑亂叫怎麼解決？</t>
+  </si>
+  <si>
+    <t>這可能是天性活動時間（黎明和黃昏）導致，也可能是精力過剩或發情行為。解決方式包括在睡前與貓進行較多的互動遊戲消耗精力，提供能獨自玩耍的玩具，並確保晚上前有足夠的進食量；若是發情導致，建議結紮以減少夜間吵鬧行為。</t>
+  </si>
+  <si>
+    <t>寵物會偷翻垃圾桶怎麼辦？</t>
+  </si>
+  <si>
+    <t>翻垃圾通常是尋找食物或好奇。解決辦法包括使用有蓋且不易被打開的垃圾桶、將垃圾桶放在櫃子或高處、固定垃圾桶避免傾倒；同時確保寵物有足夠的食物與玩具，降低因無聊而翻找垃圾的動機。</t>
+  </si>
+  <si>
+    <t>狗狗散步時會拉繩怎麼糾正？</t>
+  </si>
+  <si>
+    <t>拉繩可能是興奮或急於探索。可使用胸背帶搭配短牽繩，當狗狗拉扯時立即停下不前進，等牠回到你身邊或牽繩鬆弛時再繼續走，重複多次讓牠明白拉扯無法達到目的。結合口令如「慢慢」與獎勵可以加快學習效果。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會咬人？</t>
+  </si>
+  <si>
+    <t>可能是玩心過大、過度刺激、警戒防禦或疼痛反應。需觀察牠咬人前的肢體信號（尾巴急甩、耳朵後貼、瞳孔放大），提前停止互動；提供合適的咬咬玩具取代手，避免用手直接與貓咪激烈玩耍。若咬人是因疼痛，應立即檢查身體狀況並就醫。</t>
+  </si>
+  <si>
+    <t>狗狗為什麼會護食？</t>
+  </si>
+  <si>
+    <t>護食是源於資源保護的本能。改善方法是在平時餵食時偶爾用手添加美味的食物，讓牠習慣有人靠近時有好事發生；避免突然奪走牠的食物，逐步練習交換物品，建立「給我」的指令與互信。若護食嚴重且伴隨攻擊行為，需在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼會躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏可能是正常的休息偏好，也可能因環境變化、壓力、害怕或生病。若躲藏時間不長且仍正常飲食、排泄與互動，多屬正常；若長時間不出來或伴隨食慾下降、精神萎靡，應就醫檢查，並在家中提供安全且安靜的藏身空間。</t>
+  </si>
+  <si>
+    <t>狗狗會拆家怎麼辦？</t>
+  </si>
+  <si>
+    <t>拆家通常是精力過剩、分離焦慮或無聊造成。可透過增加每日運動量、提供可咬玩具、益智食物球等方式轉移注意力，並在外出前先帶牠消耗體力。若是分離焦慮，可逐步練習短時間離開、建立安全區域，並在外出時提供能安撫情緒的物品（如帶有主人氣味的毛巾）。</t>
+  </si>
+  <si>
+    <t>帶寵物外出前應該準備什麼？</t>
+  </si>
+  <si>
+    <t>外出前應準備牠平時習慣的食物和水、折疊碗、牽繩或胸背帶、排泄用品（尿墊或便袋）、簡單的醫療用品（止血粉、紗布）、健康證明與疫苗紀錄，以及能讓牠安心的熟悉玩具或毯子，確保牠在陌生環境中有安全感。</t>
+  </si>
+  <si>
+    <t>寵物在車上容易暈車怎麼辦？</t>
+  </si>
+  <si>
+    <t>出發前 3–4 小時避免餵食，保持車內通風與舒適溫度，讓牠能看見外部景色或固定在安全座椅上，減少搖晃感；可攜帶毛巾或墊子吸收異味，若暈車嚴重，可事先諮詢獸醫使用暈車藥。</t>
+  </si>
+  <si>
+    <t>帶寵物搭火車或高鐵需要注意什麼？</t>
+  </si>
+  <si>
+    <t>需將寵物放置於符合規格的運輸籠內，並確保籠內鋪好吸水墊與透氣良好；不同交通工具對尺寸與重量有限制，出發前應先查詢相關規定，並提前到站預留時間辦理手續。</t>
+  </si>
+  <si>
+    <t>寵物第一次出門可能會很緊張，怎麼減輕牠的焦慮？</t>
+  </si>
+  <si>
+    <t>可在出門前幾天讓牠熟悉運輸籠或胸背帶，並短時間帶到附近走走，逐步增加外出時間與距離；外出時使用熟悉的墊子、玩具或帶有主人氣味的物品安撫，保持語氣溫和並給予零食獎勵。</t>
+  </si>
+  <si>
+    <t>旅行中如何確保寵物安全？</t>
+  </si>
+  <si>
+    <t>外出時務必使用牽繩或胸背帶，不要讓牠單獨留在車內或陌生環境；住宿時檢查房間有無危險物品或可逃脫的縫隙，並確保寵物有固定的休息區域與飲水來源。</t>
+  </si>
+  <si>
+    <t>可以帶寵物上飛機嗎？</t>
+  </si>
+  <si>
+    <t>多數航空公司允許小型寵物以隨身方式放置於座位下的專用航空箱，大型寵物則需托運至貨艙。需提前確認航空公司規範，準備健康證明與疫苗接種紀錄，並使用符合 IATA 標準的航空箱。</t>
+  </si>
+  <si>
+    <t>出國帶寵物需要辦什麼手續？</t>
+  </si>
+  <si>
+    <t>需確認目的地國家的檢疫與入境規定，通常需要健康檢查證明、狂犬病疫苗證明與植入晶片，有些國家還需隔離檢疫；程序繁瑣，建議至少提前 3–6 個月準備。</t>
+  </si>
+  <si>
+    <t>寵物在外面走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即在當地尋找，並向附近動物醫院、收容所與警察報案，同時張貼協尋公告或在社群平台發布訊息。若寵物有晶片與名牌，可以大大提高被找回的機率。</t>
+  </si>
+  <si>
+    <t>旅途中寵物突然生病該怎麼處理？</t>
+  </si>
+  <si>
+    <t>應隨身攜帶緊急醫療用品與當地獸醫院清單，若出現嘔吐、腹瀉、呼吸急促等症狀，先讓牠休息並保持水分，情況持續或惡化就立即送醫；旅行前可事先詢問主治獸醫是否需要攜帶備用藥物。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些額外花費需要考慮？</t>
+  </si>
+  <si>
+    <t>除了交通與住宿費外，還需考慮寵物友善飯店的額外清潔費、交通運輸附加費（火車、飛機托運費）、臨時醫療費用、保險，以及可能需要購買的額外用品如便攜籠、可折疊水碗等。</t>
+  </si>
+  <si>
+    <t>寵物多久要做一次健康檢查？</t>
+  </si>
+  <si>
+    <t>一般建議成年犬貓每年進行一次完整健康檢查，包括體格檢查、血液檢驗、尿檢與糞檢；老年寵物（狗 7 歲以上、貓 10 歲以上）則建議每半年檢查一次，以便及早發現慢性病或器官功能退化的徵兆。</t>
+  </si>
+  <si>
+    <t>健康檢查通常包含哪些項目？</t>
+  </si>
+  <si>
+    <t>完整檢查包括體重與體態評估、牙齒與口腔檢查、眼耳鼻口觀察、皮膚與毛髮檢視、心肺聽診、腹部觸診，以及血液生化檢查、全血計數、尿液與糞便分析；必要時會進行 X 光、超音波或心電圖檢查。</t>
+  </si>
+  <si>
+    <t>血液檢查能檢測什麼？</t>
+  </si>
+  <si>
+    <t>血液檢查可以檢測紅白血球數、血紅素濃度、肝腎功能、血糖、膽固醇與電解質平衡，這些數據能幫助獸醫判斷是否有感染、貧血、代謝異常或器官疾病。</t>
+  </si>
+  <si>
+    <t>為什麼老年寵物需要更頻繁檢查？</t>
+  </si>
+  <si>
+    <t>老年寵物的器官功能下降速度較快，且慢性病（如腎臟病、心臟病、糖尿病）在早期症狀不明顯，透過半年一次的檢查能更早發現並開始治療，延長健康壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>日常保健應該注意哪些方面？</t>
+  </si>
+  <si>
+    <t>日常保健包括均衡飲食、適當運動、規律作息、定期驅蟲與疫苗接種、維持口腔清潔、定期梳毛與洗澡，以及提供安全舒適的生活環境，並留意任何行為或食慾的變化。</t>
+  </si>
+  <si>
+    <t>牙齒保健有多重要？</t>
+  </si>
+  <si>
+    <t>牙齒健康直接影響進食與整體健康，牙周病會導致口臭、牙齦炎，甚至讓細菌進入血液影響心臟與腎臟。建議每週至少刷牙 2–3 次，搭配潔牙零食或玩具，並定期讓獸醫做專業洗牙。</t>
+  </si>
+  <si>
+    <t>寵物保健食品需要吃嗎？</t>
+  </si>
+  <si>
+    <t>是否需要保健品應依健康狀況與飲食營養而定，例如關節保健品（葡萄糖胺、軟骨素）適合老年或大型犬；魚油可幫助皮膚與毛髮健康；益生菌有助腸道；但須選擇專為寵物設計且經獸醫建議的產品，避免過量或不當使用。</t>
+  </si>
+  <si>
+    <t>體重控制為什麼很重要？</t>
+  </si>
+  <si>
+    <t>過重或過瘦都會影響健康，肥胖會增加關節、心肺與糖尿病的風險，過瘦則可能表示營養不足或有疾病。應透過控制飲食與增加運動來維持理想體態，並定期量體重追蹤。</t>
+  </si>
+  <si>
+    <t>有哪些疾病是健康檢查能提早發現的？</t>
+  </si>
+  <si>
+    <t>常見可提早發現的疾病包括慢性腎病、肝功能異常、糖尿病、甲狀腺功能異常、心臟病、腫瘤，以及寄生蟲感染。提早診斷意味著能更早介入治療，延緩病情惡化。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應健康檢查？</t>
+  </si>
+  <si>
+    <t>可在平時訓練牠接受簡單的身體觸碰（看牙齒、摸耳朵、檢查爪子），搭配零食獎勵，讓牠對檢查動作不害怕；外出前帶牠熟悉運輸籠或牽繩，並保持就診過程的耐心與安撫。</t>
+  </si>
+  <si>
+    <t>Q</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>寵物需要固定餵食時間嗎？</t>
+  </si>
+  <si>
+    <t>是的，固定餵食時間能幫助維持良好的腸胃規律與行為穩定。幼犬幼貓通常需要一天 3–4 餐，成年犬貓則可調整為一天 1–2 餐。固定餵食也能幫助飼主觀察食慾變化，及早發現健康問題。</t>
+  </si>
+  <si>
+    <t>乾糧與罐頭哪個比較好？</t>
+  </si>
+  <si>
+    <t>乾糧保存方便，能幫助磨牙與減少牙垢；罐頭含水量高，能增加水分攝取並對偏食寵物更有吸引力。最佳做法是依需求混合餵食，例如以乾糧為主，搭配部分罐頭或鮮食，達到營養與水分的平衡。</t>
+  </si>
+  <si>
+    <t>不建議。許多人類食物對寵物有毒或難以消化，例如巧克力、葡萄、洋蔥、大蒜、木糖醇、酒精等都可能致命。即使是安全食材，也需注意烹調方式（不能油炸、調味）與份量控制，避免造成肥胖與消化不良。</t>
+  </si>
+  <si>
+    <t>怎麼判斷飼料是否優質？</t>
+  </si>
+  <si>
+    <t>要查看成分表，優質飼料應以動物性蛋白（如雞肉、魚肉）為主要原料，避免以大量穀物或副產品為主。營養比例要符合 AAFCO 或 FEDIAF 標準，並且不含過多人工色素、香料或防腐劑。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓的飲食需要特別注意什麼？</t>
+  </si>
+  <si>
+    <t>幼年期是快速成長階段，需要高蛋白、高熱量與鈣磷比例均衡的專用飼料，幫助骨骼與免疫系統發育。切勿餵成年寵物飼料，以免營養不足影響生長。</t>
+  </si>
+  <si>
+    <t>老年寵物的飲食要怎麼調整？</t>
+  </si>
+  <si>
+    <t>老年寵物活動量下降，容易肥胖且器官功能逐漸退化，因此飲食應選擇低熱量、高纖維、易消化的配方，並增加含關節保護或腎臟支持的營養素（如葡萄糖胺、Omega-3 脂肪酸）。</t>
+  </si>
+  <si>
+    <t>寵物需要補鈣或維生素嗎？</t>
+  </si>
+  <si>
+    <t>若食用的是完整均衡的商業飼料，通常不需額外補充。若是自製鮮食，營養比例可能不均衡，則建議在獸醫指導下補充鈣質、維生素或微量元素，以避免骨骼問題或免疫力不足。</t>
+  </si>
+  <si>
+    <t>寵物喝牛奶可以嗎？</t>
+  </si>
+  <si>
+    <t>多數成年貓狗缺乏乳糖酶，喝牛奶容易造成腹瀉與腸胃不適。市面上有專為寵物設計的低乳糖或無乳糖寵物奶粉，才適合用來補充。幼年期的寵物若需要人工哺乳，必須使用專用奶粉。</t>
+  </si>
+  <si>
+    <t>肥胖寵物該怎麼飲食控制？</t>
+  </si>
+  <si>
+    <t>應選擇低熱量配方，並以「計算每日熱量需求」為基準分餐餵食，避免隨意投餵零食；可用益智食物球延長進食時間，讓寵物邊玩邊吃，減少暴食情況。同時需搭配規律運動，達到健康減重的效果。</t>
+  </si>
+  <si>
+    <t>如何確保寵物攝取足夠水分？</t>
+  </si>
+  <si>
+    <t>狗狗通常會自行飲水，但貓咪常喝得不足。建議在家中多處放置水碗，並保持水源乾淨；部分貓咪喜歡流動水，可使用飲水機；若仍攝水不足，可增加罐頭、鮮食或在乾糧中拌水，預防泌尿與腎臟疾病。</t>
+  </si>
+  <si>
+    <t>寵物會感到孤單嗎？</t>
+  </si>
+  <si>
+    <t>會。狗狗通常需要較多陪伴，長時間單獨在家容易產生分離焦慮；貓咪雖較獨立，但若缺乏互動也可能感到孤單，導致行為問題或情緒低落。</t>
+  </si>
+  <si>
+    <t>怎麼判斷寵物是否有壓力？</t>
+  </si>
+  <si>
+    <t>常見壓力表現包括食慾下降、頻繁舔毛、躲藏、異常吠叫或排泄行為。需觀察是否持續發生並找出壓力來源，例如環境變化、噪音或缺乏陪伴。</t>
+  </si>
+  <si>
+    <t>寵物會得憂鬱症嗎？</t>
+  </si>
+  <si>
+    <t>是的，長期孤單、失去同伴或重大生活改變可能導致寵物出現憂鬱症狀，如嗜睡、無精打采、失去興趣。這需要透過增加互動、提供刺激，甚至醫師建議下使用藥物來改善。</t>
+  </si>
+  <si>
+    <t>如何安撫焦慮的狗狗？</t>
+  </si>
+  <si>
+    <t>可透過規律作息、使用安撫玩具、播放輕音樂、提供隱蔽安全的小空間幫助減壓；若是分離焦慮，需循序漸進讓牠適應獨處。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼喜歡躲起來？</t>
+  </si>
+  <si>
+    <t>躲藏是貓咪的本能，能讓牠感到安全。但若過度躲藏且伴隨食慾下降或活動減少，可能是壓力或生病的訊號，需要進一步觀察與檢查。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物適應新環境？</t>
+  </si>
+  <si>
+    <t>應逐步引導，不要一次讓牠接觸整個新環境。先提供一個安靜的小空間，裡面放熟悉的毯子或玩具，等牠穩定後再擴展活動範圍。</t>
+  </si>
+  <si>
+    <t>寵物會嫉妒嗎？</t>
+  </si>
+  <si>
+    <t>會。當飼主對其他人或動物給予更多注意時，寵物可能表現出黏人、吠叫或破壞行為。應公平對待，並在互動時給予牠足夠的安全感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物無聊？</t>
+  </si>
+  <si>
+    <t>提供益智玩具、食物隱藏遊戲、定期更換玩具，並安排日常活動與訓練。對狗狗來說，戶外運動與嗅聞活動能大幅降低無聊感。</t>
+  </si>
+  <si>
+    <t>寵物會感受到飼主的情緒嗎？</t>
+  </si>
+  <si>
+    <t>會。研究顯示寵物能透過聲音、表情與肢體語言感受飼主情緒，當飼主焦慮或憂鬱時，寵物也可能出現相應的緊張行為。</t>
+  </si>
+  <si>
+    <t>怎麼與寵物建立更好的情感連結？</t>
+  </si>
+  <si>
+    <t>透過日常陪伴、規律的互動、溫柔的撫摸與正向獎勵，讓寵物覺得與飼主相處是安全且愉快的；避免打罵與忽視，因為信任是逐步累積的。</t>
+  </si>
+  <si>
+    <t>家中有哪些東西對寵物有毒？</t>
+  </si>
+  <si>
+    <t>常見有毒食物包括巧克力、洋蔥、大蒜、葡萄、木糖醇、酒精；常見有毒植物包括百合、杜鵑、聖誕紅、滴水觀音；清潔劑、殺蟲劑、藥物等也非常危險。應將這些物品妥善收納，避免寵物誤食。</t>
+  </si>
+  <si>
+    <t>如何防止寵物咬電線？</t>
+  </si>
+  <si>
+    <t>電線應收納於防咬管內或固定在牆角，避免外露；可在電線表面噴灑苦味劑降低咬的慾望，並提供適合的咬咬玩具滿足咀嚼需求。若發現有觸電風險，務必立即檢查環境並更換受損線材。</t>
+  </si>
+  <si>
+    <t>陽台或窗戶對寵物有危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，貓狗都有可能因追逐或好奇而墜落。建議安裝防護網或堅固的紗窗，並避免在窗邊放置可攀爬的家具，降低危險。</t>
+  </si>
+  <si>
+    <t>寵物會誤食小物品嗎？</t>
+  </si>
+  <si>
+    <t>會。鈕扣、橡皮筋、塑膠袋、髮圈、玩具零件都有可能被誤食，造成腸道阻塞。建議避免將這些小物品放在地面或寵物可觸及的地方。</t>
+  </si>
+  <si>
+    <t>如何避免寵物接觸化學清潔劑？</t>
+  </si>
+  <si>
+    <t>清潔劑與殺蟲劑應放在高處或鎖櫃內，使用後確保地板完全乾燥再讓寵物進入。若不慎接觸，應立即以大量清水沖洗並送醫。</t>
+  </si>
+  <si>
+    <t>廚房對寵物來說危險嗎？</t>
+  </si>
+  <si>
+    <t>是的，廚房有熱爐、油鍋、刀具與容易掉落的食物。建議用防護門隔離廚房，或在烹飪時避免寵物進入，降低燙傷與誤食風險。</t>
+  </si>
+  <si>
+    <t>家具需要特別注意嗎？</t>
+  </si>
+  <si>
+    <t>需要。尖角家具容易造成撞傷，可用護角套保護；搖晃不穩的櫃子應固定在牆上，避免寵物攀爬時傾倒；玻璃桌面應使用防滑墊避免碎裂。</t>
+  </si>
+  <si>
+    <t>如何讓寵物在家裡有安全活動空間？</t>
+  </si>
+  <si>
+    <t>應提供一個專屬區域，放置食盆、水碗、床墊與玩具，避免危險物品接觸，讓寵物能自由活動又安全。對於幼犬幼貓，可用圍欄或籠子限制活動範圍。</t>
+  </si>
+  <si>
+    <t>發生居家意外時該怎麼處理？</t>
+  </si>
+  <si>
+    <t>第一步先保持冷靜，評估傷勢並立即進行簡單急救（如止血、沖洗），同時盡快聯絡獸醫或送醫。日常應該把附近的動物醫院與急診電話記下來，遇到緊急狀況才能迅速行動。</t>
+  </si>
+  <si>
+    <t>狗狗最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>狗狗常見的傳染病包括犬瘟熱、犬細小病毒、犬傳染性肝炎與狂犬病，這些疾病多數致死率高且傳染力強，因此定期接種疫苗是最有效的預防方式。</t>
+  </si>
+  <si>
+    <t>貓咪最常見的傳染病有哪些？</t>
+  </si>
+  <si>
+    <t>貓咪常見的傳染病包括貓瘟（泛白血球減少症）、貓皰疹病毒、貓杯狀病毒、貓白血病與狂犬病。其中部分可透過疫苗預防，飼主應依獸醫建議完成接種。</t>
+  </si>
+  <si>
+    <t>牙周病為什麼在寵物中很常見？</t>
+  </si>
+  <si>
+    <t>牙周病是因為牙菌斑與牙石累積導致牙齦發炎、口臭，嚴重時甚至造成牙齒脫落與細菌入血影響心臟與腎臟。因多數飼主忽略刷牙與口腔保健，所以牙周病成為犬貓最常見的慢性疾病之一。</t>
+  </si>
+  <si>
+    <t>寵物肥胖會引起哪些問題？</t>
+  </si>
+  <si>
+    <t>肥胖會增加關節炎、糖尿病、呼吸困難、心臟病與肝臟疾病的風險，還會縮短壽命。最有效的預防方式是控制飲食熱量、避免過量零食，並搭配適度運動維持理想體態。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼常得泌尿系統疾病？</t>
+  </si>
+  <si>
+    <t>貓咪天生飲水量低，容易導致尿液濃縮，進而產生膀胱炎、尿結晶或泌尿阻塞。預防方法包括增加水源數量、提供流動飲水器，以及餵食含水量高的罐頭或鮮食。</t>
+  </si>
+  <si>
+    <t>心絲蟲是什麼？狗貓都會得嗎？</t>
+  </si>
+  <si>
+    <t>心絲蟲是蚊子傳播的寄生蟲，會寄生在心臟與肺動脈，導致心肺衰竭甚至死亡。狗狗感染率最高，但貓咪也可能感染。預防方式是定期使用心絲蟲預防藥物（口服或滴劑），尤其在蚊蟲活躍季節更要確實投藥。</t>
+  </si>
+  <si>
+    <t>腎臟病為什麼在貓咪特別常見？</t>
+  </si>
+  <si>
+    <t>貓咪腎臟對水分濃縮的負擔大，長期下來容易造成慢性腎衰竭。此病通常在老年期出現，初期症狀不明顯。定期健康檢查、充足飲水與均衡飲食是最佳預防方式。</t>
+  </si>
+  <si>
+    <t>跳蚤與壁蝨會造成什麼影響？</t>
+  </si>
+  <si>
+    <t>跳蚤會引起皮膚過敏、貧血與絛蟲感染，壁蝨則可能傳播萊姆病或巴貝西蟲等血液寄生蟲。預防方式是定期使用驅蟲藥、保持環境清潔、避免草叢長時間停留。</t>
+  </si>
+  <si>
+    <t>哪些疾病是可以透過疫苗完全避免的？</t>
+  </si>
+  <si>
+    <t>狂犬病、犬瘟熱、犬細小、貓瘟等疾病，都能透過完整的疫苗程序大幅降低感染風險。定期追蹤追加疫苗是預防這些高致死率疾病的關鍵。</t>
+  </si>
+  <si>
+    <t>日常要怎麼預防寵物生病？</t>
+  </si>
+  <si>
+    <t>日常預防包括均衡飲食、保持運動量、定期驅蟲與疫苗接種、維持口腔與皮膚清潔、提供乾淨飲水與安全環境，並定期健康檢查。最重要的是飼主需細心觀察，當寵物出現食慾、行為或排泄異常時，應立即就醫。</t>
+  </si>
+  <si>
+    <t>寵物為什麼需要運動？</t>
+  </si>
+  <si>
+    <t>運動能幫助消耗體力、保持體態、促進心肺與關節健康，同時還能刺激腦部發展，降低焦慮與破壞行為。缺乏運動的寵物容易肥胖，也可能因壓力過大出現吠叫、抓咬家具等問題。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要多少運動量？</t>
+  </si>
+  <si>
+    <t>依品種與體型而異，小型犬每天至少 20–30 分鐘散步，中大型犬則需要 60 分鐘以上活動，牧羊犬或哈士奇等高能量犬種甚至需要 2 小時以上的戶外活動，才能消耗足夠精力。</t>
+  </si>
+  <si>
+    <t>貓咪也需要運動嗎？</t>
+  </si>
+  <si>
+    <t>需要。雖然貓咪多數時間在睡覺，但牠們仍需透過遊戲來模擬狩獵行為。每日安排 10–15 分鐘的互動遊戲（逗貓棒、滾動小球）可維持肌肉健康並減少肥胖。</t>
+  </si>
+  <si>
+    <t>有哪些適合狗狗的遊戲？</t>
+  </si>
+  <si>
+    <t>常見遊戲包括接球、拔河、嗅聞尋找零食、游泳與敏捷訓練。這些遊戲能滿足狗狗的探索慾望與運動需求，同時也能強化飼主與狗狗之間的互動關係。</t>
+  </si>
+  <si>
+    <t>有哪些適合貓咪的遊戲？</t>
+  </si>
+  <si>
+    <t>逗貓棒、羽毛玩具、滾動小球、隧道、益智餵食器都是貓咪喜歡的遊戲。重要的是模擬「捕獵循環」（潛行→追逐→撲抓→滿足），讓貓咪發洩天性並獲得心理滿足。</t>
+  </si>
+  <si>
+    <t>下雨天或室內空間有限，怎麼讓狗狗活動？</t>
+  </si>
+  <si>
+    <t>可以利用走廊或客廳進行拔河、藏食遊戲、學習新指令，或使用跑步機讓狗狗運動。還能設計室內障礙路線（如椅子、靠墊）讓狗狗穿越，刺激身體與大腦。</t>
+  </si>
+  <si>
+    <t>益智玩具對寵物有幫助嗎？</t>
+  </si>
+  <si>
+    <t>有。益智玩具能讓寵物動腦思考，獲得食物獎勵，既能減少無聊，也能改善焦慮行為。尤其對需要長時間獨處的寵物來說，益智玩具是重要的心理刺激來源。</t>
+  </si>
+  <si>
+    <t>老年寵物適合什麼運動？</t>
+  </si>
+  <si>
+    <t>老年寵物仍需要運動，但強度需降低。散步應改為短距離多次，避免劇烈奔跑與跳躍；游泳是非常好的低衝擊運動，能強化肌肉又不傷關節。</t>
+  </si>
+  <si>
+    <t>運動過度會有危險嗎？</t>
+  </si>
+  <si>
+    <t>會。若運動過度可能導致中暑、肌肉拉傷、關節損傷或心臟問題。應依寵物的年齡、健康狀況與品種調整運動量，運動中若出現喘不過氣或行動遲緩，應立即休息。</t>
+  </si>
+  <si>
+    <t>如何透過遊戲增進飼主與寵物的感情？</t>
+  </si>
+  <si>
+    <t>遊戲不僅能消耗體力，更是建立信任的重要方式。透過接球、拔河或逗貓互動，飼主能讓寵物感受到陪伴與快樂；遊戲時應使用正向鼓勵，避免責罵或強迫，讓寵物覺得與主人相處是快樂的事。</t>
+  </si>
+  <si>
+    <t>狗狗喜歡亂吠叫怎麼辦？</t>
+  </si>
+  <si>
+    <t>先找出吠叫原因，可能是警戒、無聊、焦慮或想要關注。處理方式包括增加日常運動消耗精力、遮蔽窗外刺激、用「安靜」口令搭配獎勵訓練，避免在狗狗吠叫時給予注意或食物，以免強化行為。</t>
+  </si>
+  <si>
+    <t>貓咪亂抓家具怎麼解決？</t>
+  </si>
+  <si>
+    <t>貓咪抓東西是本能，需要釋放。解決方式是提供合適的抓板或貓樹，並放置在牠常抓的地方，當牠使用時給予獎勵；同時在家具上貼雙面膠或保護膜降低吸引力，逐漸引導到正確位置。</t>
+  </si>
+  <si>
+    <t>狗狗會撲人，要如何矯正？</t>
+  </si>
+  <si>
+    <t>撲人通常是為了打招呼或博取注意。當狗狗撲人時應立即轉身忽視，不要推開牠，等牠四腳著地再給獎勵。可同時訓練「坐下」作為替代行為，讓牠學會用安靜方式迎接主人。</t>
+  </si>
+  <si>
+    <t>貓咪咬人怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪咬人可能是因為過度刺激或把手當玩具。避免用手直接與貓咪玩耍，改用逗貓棒、玩具分散注意力。若出現咬人傾向，應觀察牠是否有壓力或疼痛，必要時就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗會護食怎麼改善？</t>
+  </si>
+  <si>
+    <t>護食是資源保護本能。矯正方式是逐步建立信任：在牠吃飯時偶爾添加美味食物，讓牠習慣人靠近時有好事發生；避免直接搶食，並訓練「給我」或「放下」口令。嚴重護食應在專業訓練師指導下進行。</t>
+  </si>
+  <si>
+    <t>寵物會亂尿尿怎麼辦？</t>
+  </si>
+  <si>
+    <t>首先排除是否有泌尿道疾病。若是行為問題，需重新建立定點如廁習慣：在正確位置排泄時給予獎勵，錯誤地點則立即清理氣味，避免殘留。貓咪的話要確保貓砂盆數量足夠且保持乾淨。</t>
+  </si>
+  <si>
+    <t>狗狗會咬家具或鞋子，該怎麼辦？</t>
+  </si>
+  <si>
+    <t>通常是無聊、長牙或焦慮。應提供適合的咬咬玩具或益智玩具轉移注意力，並增加陪伴與運動時間。若已咬錯物品，應冷靜制止並給予正確替代物。</t>
+  </si>
+  <si>
+    <t>寵物分離焦慮怎麼解決？</t>
+  </si>
+  <si>
+    <t>分離焦慮表現為獨處時吠叫、破壞或排泄異常。矯正方式是循序漸進練習獨處，先短暫離開幾分鐘，逐步延長時間，並提供安撫玩具或帶有主人味道的物品。必要時可與獸醫討論行為治療或藥物輔助。</t>
+  </si>
+  <si>
+    <t>貓咪半夜吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>貓咪屬夜行性，但過度吵鬧多與精力過剩或發情有關。解決方式是睡前多陪牠玩耍消耗體力，並提供益智餵食器延長進食時間。若是因發情導致，建議考慮結紮。</t>
+  </si>
+  <si>
+    <t>狗狗會撿路邊東西吃，如何矯正？</t>
+  </si>
+  <si>
+    <t>這是危險行為，可能誤食毒物。矯正方式是訓練「放下」與「不要碰」口令，在散步時使用短牽繩控制，當狗狗嘗試撿東西時立即制止，並在遵從指令後給予獎勵，以建立良好習慣。</t>
+  </si>
+  <si>
+    <t>寵物與小孩的相處</t>
+  </si>
+  <si>
+    <t>研究顯示，與寵物共同成長的小孩在情感發展、責任感培養與同理心建立上都有正面影響。同時，與寵物互動能幫助小孩釋放壓力，甚至降低焦慮感與孤獨感。</t>
+  </si>
+  <si>
+    <t>寵物對小孩會有健康上的風險嗎？</t>
+  </si>
+  <si>
+    <t>可能存在過敏、抓咬傷或人畜共通疾病（如弓形蟲、狂犬病）的風險。只要定期驅蟲、接種疫苗、保持環境清潔並教導小孩正確互動方式，就能大幅降低風險。</t>
+  </si>
+  <si>
+    <t>小孩應該幾歲開始可以和寵物互動？</t>
+  </si>
+  <si>
+    <t>一般建議三歲以上的小孩比較能理解「溫柔觸摸」與「尊重界限」。年紀更小的孩子也能接觸寵物，但必須全程由大人監護，避免拉尾巴、戳眼睛等可能引起寵物攻擊的行為。</t>
+  </si>
+  <si>
+    <t>如何教小孩正確對待寵物？</t>
+  </si>
+  <si>
+    <t>要讓小孩學會用輕柔的手勢撫摸，不要大喊大叫或追逐寵物，並理解寵物需要安靜的空間。可以用遊戲方式教導，例如讓小孩當「小飼主」協助準備食物或換水，培養尊重與責任感。</t>
+  </si>
+  <si>
+    <t>怎麼避免寵物傷害小孩？</t>
+  </si>
+  <si>
+    <t>首先要確保寵物的性情穩定，並進行基礎訓練。避免在寵物進食或睡覺時讓小孩打擾，同時給寵物設置一個「安全空間」，當牠想休息時可以自行退避。</t>
+  </si>
+  <si>
+    <t>小孩與寵物玩耍時要注意什麼？</t>
+  </si>
+  <si>
+    <t>必須全程由大人監護，避免粗暴的動作或危險玩具。應安排安全的互動方式，例如丟球讓狗狗撿回、使用逗貓棒與貓咪互動，而不是直接用手與寵物接觸過於激烈的遊戲。</t>
+  </si>
+  <si>
+    <t>小孩若被寵物抓傷或咬傷該怎麼辦？</t>
+  </si>
+  <si>
+    <t>立即用清水和肥皂徹底清洗傷口，並用消毒液處理；若傷口嚴重或寵物疫苗未完整接種，應立即就醫，必要時接種破傷風與狂犬病疫苗。事後也要檢討原因，避免相同情況再發生。</t>
+  </si>
+  <si>
+    <t>寵物的毛會影響小孩健康嗎？</t>
+  </si>
+  <si>
+    <t>部分小孩可能對寵物毛髮或皮屑過敏，症狀包括打噴嚏、咳嗽或皮膚搔癢。可以透過定期梳毛、清潔家中環境、使用空氣清淨機來降低影響。若症狀嚴重，需考慮醫師建議與生活環境調整。</t>
+  </si>
+  <si>
+    <t>寵物會影響小孩的免疫力嗎？</t>
+  </si>
+  <si>
+    <t>有研究指出，與寵物共同生活的小孩在早期接觸到一定量的微生物，有助於免疫系統發展，甚至能降低過敏與氣喘的發生率。不過，前提是寵物健康且環境衛生維持良好。</t>
+  </si>
+  <si>
+    <t>如何讓小孩與寵物建立深厚的情感？</t>
+  </si>
+  <si>
+    <t>透過日常參與照顧，如餵食、梳毛、帶散步，讓小孩感受到自己對寵物的重要性。同時鼓勵小孩用溫柔的語氣與寵物說話，並透過遊戲或訓練建立互信，這樣能讓小孩與寵物之間形成長久的情感連結。</t>
+  </si>
+  <si>
+    <t>家裡有寵物怎麼保持整潔？</t>
+  </si>
+  <si>
+    <t>應建立固定的清潔習慣，例如每天清理寵物毛髮、每週徹底吸塵，並定期洗滌寵物的床墊、毯子與玩具。使用 HEPA 濾網的吸塵器能有效過濾細小毛屑，搭配空氣清淨機能保持空氣清新。</t>
+  </si>
+  <si>
+    <t>寵物掉毛怎麼處理？</t>
+  </si>
+  <si>
+    <t>每天梳毛能減少散落的毛髮，並促進血液循環。換季掉毛特別嚴重時，可使用專用除毛刷、黏毛滾筒或吸毛機。家具和衣物可用靜電除毛刷或專用洗衣袋處理。</t>
+  </si>
+  <si>
+    <t>家裡有寵物會有異味，怎麼解決？</t>
+  </si>
+  <si>
+    <t>應保持環境通風，定期清洗寵物廁所、籠子與睡墊。使用中性清潔劑或專用除臭噴霧，避免含氨清潔劑以免刺激寵物。貓砂需每日清理，並每週更換整盆。</t>
+  </si>
+  <si>
+    <t>寵物的餐具要多久清洗一次？</t>
+  </si>
+  <si>
+    <t>建議每天清洗一次，並使用溫水與中性洗劑，避免油垢或細菌殘留。水碗應每日更換乾淨水，並同時清潔碗具以防止黴菌或生物膜滋生。</t>
+  </si>
+  <si>
+    <t>寵物上沙發或床會影響衛生嗎？</t>
+  </si>
+  <si>
+    <t>會。寵物毛髮、皮屑和泥土容易殘留在布料上。可使用專用沙發布或毛毯保護，並定期清洗；若希望減少接觸，應建立規矩讓寵物僅使用自己的床墊。</t>
+  </si>
+  <si>
+    <t>如何處理寵物意外排泄？</t>
+  </si>
+  <si>
+    <t>應立即用紙巾或布擦拭，再用酵素型清潔劑分解尿液中的蛋白質，避免殘留氣味吸引寵物再次在相同地點排泄。切勿僅用漂白水，因為寵物仍能嗅出氣味。</t>
+  </si>
+  <si>
+    <t>寵物玩具需要清洗嗎？</t>
+  </si>
+  <si>
+    <t>需要。布製玩具建議每週用溫和洗劑清洗一次，塑膠或橡膠玩具可用清水沖洗並自然晾乾。清潔不僅能減少異味，也能預防細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物廁所要多久清理一次？</t>
+  </si>
+  <si>
+    <t>狗狗尿墊應每日更換，貓砂則建議每天鏟除排泄物，每週或依產品建議更換整盆。若環境不潔，容易導致寵物抗拒如廁或出現泌尿道疾病。</t>
+  </si>
+  <si>
+    <t>如何減少家中過敏源？</t>
+  </si>
+  <si>
+    <t>除了定期清潔毛髮外，建議使用 HEPA 空氣清淨機、每週清洗床單被套、避免讓寵物進入臥室。對過敏體質的飼主，可以與醫師討論是否需要額外過敏治療。</t>
+  </si>
+  <si>
+    <t>有哪些清潔用品對寵物安全？</t>
+  </si>
+  <si>
+    <t>選擇中性或專為寵物設計的清潔劑，避免含有氨水、氯、苯酚等強烈化學成分，因為這些成分對寵物的皮膚、呼吸道甚至肝腎有潛在危害。建議清潔後徹底沖洗乾淨並保持通風。</t>
+  </si>
+  <si>
+    <t>寵物誤食塑膠、布料或玩具怎麼辦？</t>
+  </si>
+  <si>
+    <t>不要嘗試用手硬拉，因為可能造成喉嚨或腸道受傷。應立即觀察是否有嘔吐、腹痛、食慾不振或便秘等症狀，並盡快送醫做 X 光或超音波檢查。異物可能需要內視鏡或手術移除，延誤會導致腸阻塞甚至腸穿孔。</t>
+  </si>
+  <si>
+    <t>寵物跌落高處後該怎麼處理？</t>
+  </si>
+  <si>
+    <t>跌落後可能造成骨折、內出血或胸腔損傷。應避免隨意搬動，若必須移動，盡量保持身體平直並用硬板托運。送醫前觀察是否有呼吸急促、牙齦蒼白或失去意識，這些都是危險徵兆。</t>
+  </si>
+  <si>
+    <t>寵物被其他動物咬傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>動物咬傷容易引起深層感染。應立即用清水或生理食鹽水沖洗傷口，避免使用雙氧水過度刺激，並用紗布包紮止血。即使傷口不大，也應就醫，因為咬傷常伴隱藏性膿腫或破傷風風險。</t>
+  </si>
+  <si>
+    <t>寵物指甲折斷或出血怎麼辦？</t>
+  </si>
+  <si>
+    <t>若斷裂導致出血，可用止血粉或麵粉輕壓止血，再用紗布包覆。避免讓寵物舔咬傷口，以免感染。若斷裂處過深或反覆出血，應由獸醫修整並處理，避免甲床感染</t>
+  </si>
+  <si>
+    <t>寵物眼睛突然紅腫流淚怎麼辦？</t>
+  </si>
+  <si>
+    <t>可能是異物、角膜潰瘍或急性青光眼。可先用生理食鹽水輕柔沖洗異物，但若眼睛持續紅腫或分泌物增多，應立即送醫，因為角膜潰瘍惡化很快，延誤可能導致永久失明。</t>
+  </si>
+  <si>
+    <t>寵物耳朵突然流膿或甩頭不停怎麼處理？</t>
+  </si>
+  <si>
+    <t>這可能是耳炎或耳血腫。不要自行用棉花棒深入耳道，以免推擠更深。可先用濕布清理外耳分泌物，並戴上頭套防止抓耳，接著送醫檢查耳道，必要時做耳鏡檢查與藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物被蜜蜂或昆蟲螫到怎麼辦？</t>
+  </si>
+  <si>
+    <t>若有毒針殘留，用鑷子或信用卡邊緣輕輕刮除，再用冷敷減輕腫脹。若寵物出現呼吸困難、臉部快速腫脹、全身無力，可能是過敏性休克，應立即送醫。</t>
+  </si>
+  <si>
+    <t>寵物抽筋但不是癲癇怎麼處理？</t>
+  </si>
+  <si>
+    <t>抽筋可能來自電解質不平衡、肌肉痙攣或中毒。應先讓寵物安靜休息，避免觸碰抽搐部位，以免受傷。觀察是否伴隨嘔吐、虛弱或失去意識，並盡快就醫做血液檢查，確認是否需要補液或矯正電解質。</t>
+  </si>
+  <si>
+    <t>寵物尾巴或四肢被夾傷怎麼辦？</t>
+  </si>
+  <si>
+    <t>夾傷可能造成骨折或神經損傷。應先檢查是否有出血，若有則加壓止血，再輕輕固定患肢，避免寵物自行舔咬。即使外表無明顯出血，也可能有骨折或神經受損，仍需送醫做影像學檢查。</t>
+  </si>
+  <si>
+    <t>寵物突然呼吸困難該怎麼辦？</t>
+  </si>
+  <si>
+    <t>呼吸困難可能來自哽塞、哮喘、胸腔積液或心臟病。此時不要強迫餵食或灌水，應保持安靜與通風，避免過度搬動，盡快送往動物醫院。若寵物完全無法呼吸，可在送醫途中依照正確方式實施 CPR。</t>
+  </si>
+  <si>
+    <t>多久要幫寵物梳毛？</t>
+  </si>
+  <si>
+    <t>短毛犬貓可每週 2–3 次，長毛品種則最好每天梳理。梳毛能減少掉毛、避免毛球或毛打結，並促進血液循環。建議使用適合毛長的梳子，例如針梳、排梳或脫毛梳。</t>
+  </si>
+  <si>
+    <t>幫寵物洗澡的頻率應該多久一次？</t>
+  </si>
+  <si>
+    <t>狗狗一般建議每 3–4 週洗一次，長毛或有皮膚問題的狗可能需要更頻繁；貓咪通常不需要定期洗澡，除非特別髒或有皮膚病。洗澡時應使用專用寵物沐浴乳，避免用人類洗髮精。</t>
+  </si>
+  <si>
+    <t>指甲要多久修剪一次？</t>
+  </si>
+  <si>
+    <t>平均每 3–4 週修剪一次，觀察指甲是否過長以致走路時會發出「喀喀」聲或卡到地板。修剪時要避開血線（粉紅色區域），若不小心剪到出血，可用止血粉或玉米粉止血。</t>
+  </si>
+  <si>
+    <t>耳朵需要清潔嗎？</t>
+  </si>
+  <si>
+    <t>需要。建議每 2–4 週檢查一次耳朵，若有耳垢或異味，可用專用耳液滴入後輕柔按摩耳根，再用棉球擦拭外耳。不要用棉花棒深入耳道，以免推擠耳垢或傷害耳膜。</t>
+  </si>
+  <si>
+    <t>寵物的牙齒要怎麼保養？</t>
+  </si>
+  <si>
+    <t>最有效的方法是刷牙，建議每週至少 2–3 次，使用寵物專用牙刷與牙膏。可搭配潔牙零食或潔牙玩具減少牙垢。定期獸醫洗牙能有效預防牙周病與口臭。</t>
+  </si>
+  <si>
+    <t>寵物的眼睛需要特別照護嗎？</t>
+  </si>
+  <si>
+    <t>應定期檢查是否有分泌物或紅腫。輕微分泌物可用溫水或無刺激的眼部清潔液擦拭。淚痕可用專用濕紙巾清理。若出現大量分泌物或持續紅腫，應盡快就醫。</t>
+  </si>
+  <si>
+    <t>如何保持寵物的腳掌清潔？</t>
+  </si>
+  <si>
+    <t>外出回家後，應用濕紙巾或溫水擦拭腳掌，保持乾淨，避免泥土與細菌殘留。若腳毛過長，可修剪腳墊周圍毛髮以減少打滑與細菌滋生。</t>
+  </si>
+  <si>
+    <t>寵物的床墊多久要清洗一次？</t>
+  </si>
+  <si>
+    <t>建議至少每 1–2 週清洗一次，使用中性洗劑或專用清潔劑，並徹底晾乾避免黴菌滋生。若寵物有皮膚病，建議更頻繁更換與消毒。</t>
+  </si>
+  <si>
+    <t>怎麼正確清潔寵物的用品？</t>
+  </si>
+  <si>
+    <t>食盆和水碗應每天清洗，玩具則依材質分別清潔（布製可機洗、橡膠製可溫水清洗）。建議使用中性清潔劑或寵物專用產品，避免殘留化學物質。</t>
+  </si>
+  <si>
+    <t>日常照護有哪些小秘訣？</t>
+  </si>
+  <si>
+    <t>建立固定的清潔習慣，例如「每天梳毛＋清理水碗、每週修剪指甲或檢查耳朵、每月洗澡或全面清潔用品」。透過日常小動作，不僅能保持寵物健康，也能增進飼主與寵物的互動關係。</t>
+  </si>
+  <si>
+    <t>貓咪都會喝牛奶嗎？</t>
+  </si>
+  <si>
+    <t>這是迷思。許多成年貓咪缺乏乳糖酶，喝牛奶會造成腹瀉與腸胃不適。若要補充，可以選擇市售專為貓咪設計的低乳糖或無乳糖寵物奶粉。</t>
+  </si>
+  <si>
+    <t>狗狗吃大蒜能驅蟲嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。大蒜對狗狗（以及貓咪）有毒，會破壞紅血球造成貧血。驅蟲應使用獸醫推薦的專用藥物，而不是人類的食材或偏方。</t>
+  </si>
+  <si>
+    <t>貓咪摔下來總是能四腳著地嗎？</t>
+  </si>
+  <si>
+    <t>雖然貓咪有「翻正反射」，通常能在空中扭轉身體，但並非每次都能完美落地。若高度過低或過高，都可能造成骨折或內臟傷害，因此家中陽台與窗戶必須加裝防護網。</t>
+  </si>
+  <si>
+    <t>狗狗流鼻子濕就是健康的嗎？</t>
+  </si>
+  <si>
+    <t>鼻子濕潤不一定代表健康，乾燥也不一定表示生病。狗狗健康與否應觀察精神、食慾、排泄與體溫，而不是僅靠鼻子的濕潤程度來判斷。</t>
+  </si>
+  <si>
+    <t>貓咪懷孕一定要生小貓嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。很多飼主以為懷孕後貓咪必須繁殖，但事實上貓咪可以透過結紮避免懷孕，既能降低流浪貓數量，也能減少子宮蓄膿與乳腺腫瘤的風險。</t>
+  </si>
+  <si>
+    <t>小型犬不需要運動嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。雖然小型犬活動量較低，但仍需要每日散步與遊戲來維持心理與身體健康。缺乏運動會導致肥胖與行為問題。</t>
+  </si>
+  <si>
+    <t>寵物吃骨頭對牙齒有好處嗎？</t>
+  </si>
+  <si>
+    <t>部分骨頭（特別是熟骨頭）容易碎裂，會刮傷口腔、刺穿腸胃，甚至造成腸阻塞。若要幫助清潔牙齒，應選擇專業潔牙骨或潔牙玩具，而非隨意餵食骨頭。</t>
+  </si>
+  <si>
+    <t>狗狗舔傷口能幫助傷口癒合嗎？</t>
+  </si>
+  <si>
+    <t>雖然狗狗唾液含有少量抗菌物質，但過度舔舐反而會導致感染或延遲癒合。若寵物受傷，應清潔傷口並包紮，必要時戴上伊莉莎白頭套避免舔咬。</t>
+  </si>
+  <si>
+    <t>貓咪養在家裡就不需要打疫苗嗎？</t>
+  </si>
+  <si>
+    <t>錯誤。即使是室內貓，也可能透過人類衣物鞋子帶入病菌，或在緊急外出時暴露於風險環境。疫苗能預防致命疾病（如貓瘟），因此即使是室內貓也需要定期接種。</t>
+  </si>
+  <si>
+    <t>寵物年紀大了就不用看醫生了嗎？</t>
+  </si>
+  <si>
+    <t>完全錯誤。老年寵物更需要定期健康檢查，因為腎臟病、心臟病與腫瘤在早期常沒有明顯症狀。透過半年一次的檢查能提早發現並治療，延長壽命與生活品質。</t>
+  </si>
+  <si>
+    <t>外出旅行前要先做哪些準備？</t>
+  </si>
+  <si>
+    <t>應先確認寵物已完成疫苗與驅蟲，攜帶健康證明、醫療記錄與常用藥物。準備運輸籠、牽繩、食物、水與便用品，並在出發前讓寵物適應運輸工具，降低不安。</t>
+  </si>
+  <si>
+    <t>如何選擇安全的運輸籠？</t>
+  </si>
+  <si>
+    <t>運輸籠應堅固耐用、透氣良好，大小需讓寵物能站立、轉身與躺下。車用或飛機用運輸籠應符合 IATA 標準，門鎖牢固，內部可放置吸水墊與熟悉的毯子，增加安全感。</t>
+  </si>
+  <si>
+    <t>帶寵物搭車時要注意什麼？</t>
+  </si>
+  <si>
+    <t>切勿讓寵物自由在車內走動，避免干擾駕駛或發生意外。應使用安全帶專用胸背帶或固定的運輸籠，並保持車內通風，避免中暑。長途行駛要定時休息，讓寵物喝水與排泄。</t>
+  </si>
+  <si>
+    <t>散步時有哪些潛在危險？</t>
+  </si>
+  <si>
+    <t>常見危險包括車輛、噪音、陌生動物或有毒植物。飼主應全程使用牽繩，避免讓寵物隨意亂跑；在不熟悉的區域散步時，建議避開草叢與垃圾區，以防誤食異物或被寄生蟲叮咬。</t>
+  </si>
+  <si>
+    <t>帶寵物去公園或寵物友善場所要注意什麼？</t>
+  </si>
+  <si>
+    <t>要確認是否有寵物活動區，並遵守當地規範。應攜帶拾便袋，隨時清理排泄物。與其他寵物互動時，要觀察牠們的肢體語言，避免衝突。若寵物有攻擊傾向，應戴上口罩或避免進入人群密集區。</t>
+  </si>
+  <si>
+    <t>寵物在外住宿時怎麼確保安全？</t>
+  </si>
+  <si>
+    <t>進入住處後，先檢查房間是否有危險物品（如電線、清潔劑、窗戶縫隙），並為寵物設置專屬休息區。可攜帶牠熟悉的毯子或玩具，降低焦慮。若需單獨留在房間，最好使用運輸籠或寵物圍欄確保安全。</t>
+  </si>
+  <si>
+    <t>寵物在外出時走失怎麼辦？</t>
+  </si>
+  <si>
+    <t>應立即尋找並呼喊牠的名字，同時聯絡當地的動物醫院、收容所與警察。若寵物有晶片或名牌，能大幅增加找回機率。平時可在項圈上附上主人的電話號碼，並考慮使用 GPS 定位項圈。</t>
+  </si>
+  <si>
+    <t>外出時如何避免寵物中暑？</t>
+  </si>
+  <si>
+    <t>應避免在正午高溫時段散步，選擇早晨或傍晚外出。攜帶水瓶與便攜水碗，讓寵物隨時補水；停留在陰涼處休息，避免在高溫柏油路上行走，以免燙傷腳墊。</t>
+  </si>
+  <si>
+    <t>搭飛機時如何減輕寵物的壓力？</t>
+  </si>
+  <si>
+    <t>出發前先讓寵物熟悉航空箱，放置熟悉的毯子與玩具。起飛前避免餵食大量食物，僅給少量水。若寵物極度緊張，可諮詢獸醫使用天然鎮定劑或藥物，但需在專業指導下使用。</t>
+  </si>
+  <si>
+    <t>帶寵物旅行有哪些保險可以考慮？</t>
+  </si>
+  <si>
+    <t>市面上有寵物醫療險與旅行險，可涵蓋突發疾病、意外受傷或走失協尋等保障。若計畫長途旅行，建議提前為寵物投保，確保在外地也能獲得即時醫療與安全保障。</t>
+  </si>
+  <si>
+    <t>為什麼要訓練寵物？</t>
+  </si>
+  <si>
+    <t>訓練不只是讓寵物聽話，更能增進飼主與寵物的溝通，避免危險行為（如亂跑、咬人），並提供心理刺激。良好的訓練能讓生活更有秩序，也能提升寵物的安全與幸福感。</t>
+  </si>
+  <si>
+    <t>什麼是「正向強化」訓練？</t>
+  </si>
+  <si>
+    <t>正向強化是當寵物表現正確行為時，立即給予獎勵（零食、撫摸或口頭稱讚），讓牠將行為與好結果連結，進而增加該行為的出現頻率。這是目前最科學且有效的訓練方法。</t>
+  </si>
+  <si>
+    <t>如何教狗狗「坐下」？</t>
+  </si>
+  <si>
+    <t>先拿零食在狗狗鼻子前，慢慢往上移動，當牠自然坐下時立即獎勵，並同時說出口令「坐下」。重複練習數次，狗狗就能將動作與口令建立連結。</t>
+  </si>
+  <si>
+    <t>如何教狗狗「等待」？</t>
+  </si>
+  <si>
+    <t>讓狗狗坐下後舉起手掌，清楚說「等」。若狗狗保持不動幾秒，就給獎勵。逐步延長時間與距離，並在結束時加上「好」或「來」解除口令。這能幫助建立自控力。</t>
+  </si>
+  <si>
+    <t>如何訓練狗狗定點如廁？</t>
+  </si>
+  <si>
+    <t>應在固定時間帶狗狗到指定位置排泄，並在完成後立即獎勵。若在錯誤地點排泄，要立即清理並去除氣味，避免牠再次在同處如廁。幼犬需更頻繁帶去，建立習慣後就能逐漸穩定。</t>
+  </si>
+  <si>
+    <t>貓咪能被訓練嗎？</t>
+  </si>
+  <si>
+    <t>能。雖然貓咪不像狗狗那樣追求主人的指令，但透過零食與玩具獎勵，也能學會簡單指令（如「過來」、「高五」）。關鍵是使用短時間、多次練習，避免強迫。</t>
+  </si>
+  <si>
+    <t>如何讓寵物學會「過來」？</t>
+  </si>
+  <si>
+    <t>在家中短距離開始，蹲下呼喚名字並說「過來」，當牠靠近就立即給獎勵。可逐漸增加距離與干擾環境，最終達到在戶外也能可靠回應，這是確保安全的重要訓練。</t>
+  </si>
+  <si>
+    <t>如何讓寵物適應牽繩？</t>
+  </si>
+  <si>
+    <t>應先在家中或安靜環境讓牠熟悉胸背帶與牽繩，當牠冷靜走在旁邊時給予獎勵。若拉扯，應立刻停下不前進，等牠鬆開後再繼續走，讓牠明白拉扯無法達到目的。</t>
+  </si>
+  <si>
+    <t>寵物咬東西怎麼糾正？</t>
+  </si>
+  <si>
+    <t>不要責罵，而是提供正確的替代品（咬咬玩具）。若咬到不該咬的東西，應立即制止並引導到玩具上，當牠選擇正確物品時給獎勵，逐步建立好習慣。</t>
+  </si>
+  <si>
+    <t>訓練過程中常見的錯誤有哪些？</t>
+  </si>
+  <si>
+    <t>常見錯誤包括訓練時間過長導致寵物失去專注、口令不一致（家人用不同詞）、責罵或體罰、沒有即時獎勵。訓練應簡短（5–10 分鐘）、一致且愉快，讓寵物覺得學習是快樂的事。</t>
+  </si>
+  <si>
+    <t>寵物一定需要吃保健品嗎？</t>
+  </si>
+  <si>
+    <t>如果寵物食用的是完整均衡的商業飼料，一般不需要額外補充。但在特定情況下（如老年寵物、慢性病、挑食或鮮食飼養），可能會需要額外的營養補充劑來支持健康。是否需要，應依照獸醫評估決定。</t>
+  </si>
+  <si>
+    <t>哪些寵物適合補充魚油？</t>
+  </si>
+  <si>
+    <t>魚油含有 Omega-3 脂肪酸（EPA、DHA），能改善皮膚過敏、降低發炎、幫助心血管與腎臟健康，對皮膚癢、毛髮乾燥或老年寵物特別有益。但劑量過高可能引起腹瀉或出血傾向，需依體重精準計算。</t>
+  </si>
+  <si>
+    <t>益生菌對寵物有什麼幫助？</t>
+  </si>
+  <si>
+    <t>益生菌能幫助維持腸道菌叢平衡，改善腹瀉、便秘與腸胃敏感，特別適合換糧、壓力大或使用抗生素後的寵物。選擇時應挑選專為犬貓設計的菌株，避免使用人用益生菌，因為效果與安全性未必相同。</t>
+  </si>
+  <si>
+    <t>葡萄糖胺與軟骨素適合哪些寵物？</t>
+  </si>
+  <si>
+    <t>這些成分主要用於保護關節，能減緩關節炎退化並維持活動力。適合年長犬、體型較大的狗或有關節病史的品種（如黃金獵犬、哈士奇）。貓咪若有關節問題，也可在獸醫建議下補充。</t>
+  </si>
+  <si>
+    <t>寵物需要補充維生素嗎？</t>
+  </si>
+  <si>
+    <t>若以均衡飼料為主，一般不需要額外補充。過量補充反而可能造成中毒（如維生素 D 或鈣質過多會導致腎臟受損）。鮮食或自製餐則需在專業營養師指導下正確添加維生素與礦物質。</t>
+  </si>
+  <si>
+    <t>益智腦部保健品真的有效嗎？</t>
+  </si>
+  <si>
+    <t>針對老年犬貓，市面上有含抗氧化物質（如維生素 E、C、DHA、磷脂酰絲胺酸）的腦部保健品。這些成分能延緩認知功能退化，但效果因個體差異而異，通常作為輔助支持而非治療。</t>
+  </si>
+  <si>
+    <t>毛髮專用保健品有什麼作用？</t>
+  </si>
+  <si>
+    <t>多數含有生物素、鋅與 Omega-3，能幫助改善掉毛、皮膚乾燥與毛髮黯淡。若掉毛原因是疾病或營養不良，單靠保健品無法根治，仍需先排除病因。</t>
+  </si>
+  <si>
+    <t>免疫力保健品適合哪些寵物？</t>
+  </si>
+  <si>
+    <t>含有β-葡聚糖、牛初乳或特定維生素的免疫保健品，可幫助免疫功能較弱的寵物（如幼犬幼貓、老年寵物或術後康復期）。但應配合良好營養與醫療照護，不能取代疫苗或藥物治療。</t>
+  </si>
+  <si>
+    <t>寵物補鈣需要注意什麼？</t>
+  </si>
+  <si>
+    <t>若食用完整飼料，一般不需額外補鈣。過量補鈣可能導致骨骼變形、腎臟負擔甚至泌尿結石。只有在特定需求（如成長期、大型犬、哺乳期）或自製餐時，才需要在獸醫建議下補充。</t>
+  </si>
+  <si>
+    <t>如何正確選擇寵物保健品？</t>
+  </si>
+  <si>
+    <t>應優先選擇有獸醫推薦或經過動物實驗驗證的品牌，避免購買無標示來源或劑量的產品。要注意成分含量是否符合寵物需求，並依照體重計算正確劑量，切勿自行以人用保健品替代。</t>
   </si>
 </sst>
 </file>
@@ -1377,6 +2777,1393 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35DA7308-013B-421E-A64B-465486ED07CB}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="51.625" customWidth="1"/>
+    <col min="4" max="4" width="67.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>220</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>224</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>230</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>232</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>234</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>238</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>239</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A3B312-0DB8-4414-9879-6342BE992E27}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="33.75" customWidth="1"/>
+    <col min="4" max="4" width="55" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>240</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>250</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>252</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>254</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>259</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C2B2787-66B9-4D39-8D94-E6047BC5BA3C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="45.875" customWidth="1"/>
+    <col min="4" max="4" width="66.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>260</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>262</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>264</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>270</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>274</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>278</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8423BF09-87E9-4970-93EC-3DF86ABF7B15}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="70" customWidth="1"/>
+    <col min="4" max="4" width="63.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>280</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>286</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>290</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E067952E-C4D3-48EC-9BBE-1BC9550FB559}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="63.875" customWidth="1"/>
+    <col min="3" max="3" width="5.875" customWidth="1"/>
+    <col min="4" max="4" width="84.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>302</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>310</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>314</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>316</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>318</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>319</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4616CA0-AF7E-4D46-810F-23C87472795C}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="28.25" customWidth="1"/>
+    <col min="4" max="4" width="135.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>320</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>326</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>338</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>339</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36550ED9-6A20-4AEA-A31B-F221EE3E39D1}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="37.875" customWidth="1"/>
+    <col min="4" max="4" width="129.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>340</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>342</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>348</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>350</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>352</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>354</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>356</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>358</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>359</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E1A4E47-9EAE-4E2F-9FFF-D3D1C8ACF58E}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="24.375" customWidth="1"/>
+    <col min="4" max="4" width="142.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>360</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>362</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>364</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>366</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>374</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>376</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>379</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95B9C817-5F15-434B-B525-CCD562C42FDC}">
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="35.5" customWidth="1"/>
+    <col min="4" max="4" width="131.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
+        <v>386</v>
+      </c>
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>388</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="s">
+        <v>392</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" t="s">
+        <v>394</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" t="s">
+        <v>396</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>399</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E472085-C7D0-477C-BB11-1A3C247402AE}">
   <dimension ref="A1:D10"/>
@@ -1524,6 +4311,1018 @@
       </c>
       <c r="D10" t="s">
         <v>59</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{23F2D3AD-70BA-4273-AC19-FA97AC2DE74C}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31" customWidth="1"/>
+    <col min="2" max="2" width="154.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B3" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>407</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>413</v>
+      </c>
+      <c r="B8" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>415</v>
+      </c>
+      <c r="B9" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>417</v>
+      </c>
+      <c r="B10" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>419</v>
+      </c>
+      <c r="B11" t="s">
+        <v>420</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89D1BB2D-68B8-437A-A8BA-E4C1E09401CC}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="31.625" customWidth="1"/>
+    <col min="2" max="2" width="144.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>421</v>
+      </c>
+      <c r="B2" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>427</v>
+      </c>
+      <c r="B5" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>437</v>
+      </c>
+      <c r="B10" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B11" t="s">
+        <v>440</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54B4E845-653A-409A-811A-CE53A9D74D25}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="37.5" customWidth="1"/>
+    <col min="2" max="2" width="142.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B2" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>443</v>
+      </c>
+      <c r="B3" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>445</v>
+      </c>
+      <c r="B4" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>447</v>
+      </c>
+      <c r="B5" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>453</v>
+      </c>
+      <c r="B8" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>455</v>
+      </c>
+      <c r="B9" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>457</v>
+      </c>
+      <c r="B10" t="s">
+        <v>458</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{553FBEB8-844E-4441-8022-97463768914E}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.125" customWidth="1"/>
+    <col min="2" max="2" width="103" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B2" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>461</v>
+      </c>
+      <c r="B3" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>463</v>
+      </c>
+      <c r="B4" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>465</v>
+      </c>
+      <c r="B5" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>467</v>
+      </c>
+      <c r="B6" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B7" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>471</v>
+      </c>
+      <c r="B8" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>473</v>
+      </c>
+      <c r="B9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>475</v>
+      </c>
+      <c r="B10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>477</v>
+      </c>
+      <c r="B11" t="s">
+        <v>478</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69539DC7-94A1-4455-AD17-C3AB3AB1C62A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="89.75" customWidth="1"/>
+    <col min="2" max="2" width="91.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>479</v>
+      </c>
+      <c r="B2" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>481</v>
+      </c>
+      <c r="B3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>485</v>
+      </c>
+      <c r="B5" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B7" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>491</v>
+      </c>
+      <c r="B8" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>493</v>
+      </c>
+      <c r="B9" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>495</v>
+      </c>
+      <c r="B10" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>497</v>
+      </c>
+      <c r="B11" t="s">
+        <v>498</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{995E680F-1C3B-4FA9-8FCA-7307FD862C8D}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="60.5" customWidth="1"/>
+    <col min="2" max="2" width="116.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>501</v>
+      </c>
+      <c r="B3" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>503</v>
+      </c>
+      <c r="B4" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>505</v>
+      </c>
+      <c r="B5" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>507</v>
+      </c>
+      <c r="B6" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>509</v>
+      </c>
+      <c r="B7" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>511</v>
+      </c>
+      <c r="B8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>513</v>
+      </c>
+      <c r="B9" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>515</v>
+      </c>
+      <c r="B10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B11" t="s">
+        <v>518</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{822F957D-6D11-4C04-B808-1E122B479F35}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="63.5" customWidth="1"/>
+    <col min="2" max="2" width="96.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B2" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>521</v>
+      </c>
+      <c r="B3" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>523</v>
+      </c>
+      <c r="B4" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>525</v>
+      </c>
+      <c r="B5" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>527</v>
+      </c>
+      <c r="B6" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B7" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>531</v>
+      </c>
+      <c r="B8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>535</v>
+      </c>
+      <c r="B10" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>537</v>
+      </c>
+      <c r="B11" t="s">
+        <v>538</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A4910CF-DA54-46CF-B32C-C4613BB99E8A}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.375" customWidth="1"/>
+    <col min="2" max="2" width="103.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>545</v>
+      </c>
+      <c r="B5" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>547</v>
+      </c>
+      <c r="B6" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B7" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>551</v>
+      </c>
+      <c r="B8" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>553</v>
+      </c>
+      <c r="B9" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>555</v>
+      </c>
+      <c r="B10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>557</v>
+      </c>
+      <c r="B11" t="s">
+        <v>558</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E0FB40-F2C1-4805-8576-8A48549043AD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.375" customWidth="1"/>
+    <col min="2" max="2" width="100.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>559</v>
+      </c>
+      <c r="B2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>563</v>
+      </c>
+      <c r="B4" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>565</v>
+      </c>
+      <c r="B5" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>567</v>
+      </c>
+      <c r="B6" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>569</v>
+      </c>
+      <c r="B7" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>571</v>
+      </c>
+      <c r="B8" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>575</v>
+      </c>
+      <c r="B10" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>577</v>
+      </c>
+      <c r="B11" t="s">
+        <v>578</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD183352-C60D-40A4-8FC2-88A7FCADDB84}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="73.75" customWidth="1"/>
+    <col min="2" max="2" width="104.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>579</v>
+      </c>
+      <c r="B2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>581</v>
+      </c>
+      <c r="B3" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B4" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>585</v>
+      </c>
+      <c r="B5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>587</v>
+      </c>
+      <c r="B6" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>589</v>
+      </c>
+      <c r="B7" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>591</v>
+      </c>
+      <c r="B8" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>593</v>
+      </c>
+      <c r="B9" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>595</v>
+      </c>
+      <c r="B10" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>597</v>
+      </c>
+      <c r="B11" t="s">
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -1685,6 +5484,414 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D21220D-A8CB-405D-A443-177471D54332}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="71.25" customWidth="1"/>
+    <col min="2" max="2" width="111" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>599</v>
+      </c>
+      <c r="B2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>601</v>
+      </c>
+      <c r="B3" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>603</v>
+      </c>
+      <c r="B4" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>605</v>
+      </c>
+      <c r="B5" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>607</v>
+      </c>
+      <c r="B6" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>609</v>
+      </c>
+      <c r="B7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>611</v>
+      </c>
+      <c r="B8" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>613</v>
+      </c>
+      <c r="B9" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>617</v>
+      </c>
+      <c r="B11" t="s">
+        <v>618</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DDBC5497-E548-47C1-92AE-6F40EA344E03}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="70.875" customWidth="1"/>
+    <col min="2" max="2" width="103.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>619</v>
+      </c>
+      <c r="B2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>621</v>
+      </c>
+      <c r="B3" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>623</v>
+      </c>
+      <c r="B4" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>625</v>
+      </c>
+      <c r="B5" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>627</v>
+      </c>
+      <c r="B6" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>629</v>
+      </c>
+      <c r="B7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B8" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>633</v>
+      </c>
+      <c r="B9" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>635</v>
+      </c>
+      <c r="B10" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>637</v>
+      </c>
+      <c r="B11" t="s">
+        <v>638</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{646C2F24-950B-4A5B-BF35-AA4D88D15B44}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="62.875" customWidth="1"/>
+    <col min="2" max="2" width="109.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>639</v>
+      </c>
+      <c r="B2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>641</v>
+      </c>
+      <c r="B3" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>643</v>
+      </c>
+      <c r="B4" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>645</v>
+      </c>
+      <c r="B5" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>647</v>
+      </c>
+      <c r="B6" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>649</v>
+      </c>
+      <c r="B7" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>651</v>
+      </c>
+      <c r="B8" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>653</v>
+      </c>
+      <c r="B9" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>655</v>
+      </c>
+      <c r="B10" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>657</v>
+      </c>
+      <c r="B11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E0BD83-7A73-4F52-A26E-9E339479AF85}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="81.25" customWidth="1"/>
+    <col min="2" max="2" width="92.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>659</v>
+      </c>
+      <c r="B2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>663</v>
+      </c>
+      <c r="B4" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>667</v>
+      </c>
+      <c r="B6" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>669</v>
+      </c>
+      <c r="B7" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>671</v>
+      </c>
+      <c r="B8" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>673</v>
+      </c>
+      <c r="B9" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>675</v>
+      </c>
+      <c r="B10" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>677</v>
+      </c>
+      <c r="B11" t="s">
+        <v>678</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532B40C6-DF30-4B29-B9D0-4F29D5AC34C2}">
   <dimension ref="A1:D10"/>

--- a/寵物照護QA.xlsx
+++ b/寵物照護QA.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29325"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D74EE07-35D4-4BD0-8F58-BE89CB748E35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{769F42EF-2752-4DED-BE37-85B18897E824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="31" activeTab="32" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="38" activeTab="39" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="飼養前的準備" sheetId="1" r:id="rId1"/>
@@ -41,6 +41,13 @@
     <sheet name="寵物旅行與外出安全" sheetId="31" r:id="rId31"/>
     <sheet name="寵物訓練基礎入門" sheetId="32" r:id="rId32"/>
     <sheet name="寵物營養補充與保健品" sheetId="33" r:id="rId33"/>
+    <sheet name="寵物與人類及陌生環境的社交" sheetId="34" r:id="rId34"/>
+    <sheet name="多寵家庭與跨物種相處" sheetId="35" r:id="rId35"/>
+    <sheet name="一般睡眠與作息問題" sheetId="36" r:id="rId36"/>
+    <sheet name="特殊情況與老年寵物" sheetId="37" r:id="rId37"/>
+    <sheet name="家庭環境安全" sheetId="38" r:id="rId38"/>
+    <sheet name="災難與急難應變" sheetId="39" r:id="rId39"/>
+    <sheet name="常見慢性疾病" sheetId="40" r:id="rId40"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -63,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="818">
   <si>
     <t>Q1</t>
   </si>
@@ -2100,6 +2107,423 @@
   </si>
   <si>
     <t>應優先選擇有獸醫推薦或經過動物實驗驗證的品牌，避免購買無標示來源或劑量的產品。要注意成分含量是否符合寵物需求，並依照體重計算正確劑量，切勿自行以人用保健品替代。</t>
+  </si>
+  <si>
+    <t>為什麼寵物需要社交訓練？</t>
+  </si>
+  <si>
+    <t>社交能讓寵物學會如何安全地與人、其他動物和環境互動，避免因恐懼或焦慮產生攻擊或逃避行為。從小建立良好的社交習慣，能降低日後出現行為問題的風險。</t>
+  </si>
+  <si>
+    <t>什麼時候開始社交訓練最好？</t>
+  </si>
+  <si>
+    <t>幼犬在 3–16 週是黃金社交期，幼貓則在 2–9 週。此時應讓牠們接觸不同的人、聲音、環境與動物，並搭配正向獎勵，建立正面的經驗。</t>
+  </si>
+  <si>
+    <t>如何讓狗狗習慣陌生人？</t>
+  </si>
+  <si>
+    <t>初次接觸時避免突然撫摸或靠近，讓狗狗先主動嗅聞陌生人。當狗狗保持冷靜時，陌生人可給予零食獎勵，逐步建立對陌生人的安全感。</t>
+  </si>
+  <si>
+    <t>貓咪如何適應來訪的客人？</t>
+  </si>
+  <si>
+    <t>貓咪通常較敏感，應提供一個安靜的躲藏空間，讓牠能自行選擇是否與客人互動。客人應避免直視或主動伸手，等待貓咪自行靠近。</t>
+  </si>
+  <si>
+    <t>進入新環境時應先提供一個熟悉的小空間（例如房間內有牠的床、玩具），逐步開放更多區域。使用牠熟悉的物品能降低焦慮，讓牠逐步建立安全感。</t>
+  </si>
+  <si>
+    <t>狗狗去狗公園前要注意什麼？</t>
+  </si>
+  <si>
+    <t>確認狗狗已完成疫苗與驅蟲，且能聽從基本指令如「過來」、「坐下」。觀察狗狗是否有攻擊或過度害怕的傾向，並挑選不擁擠的時段前往，避免發生衝突。</t>
+  </si>
+  <si>
+    <t>寵物出現怕聲音（如打雷、煙火）怎麼辦？</t>
+  </si>
+  <si>
+    <t>可在平時進行脫敏訓練，例如播放低音量的聲音並搭配獎勵，逐漸提高音量。發生當下可提供安靜安全的空間，避免強迫安撫或懲罰，否則會加重焦慮。</t>
+  </si>
+  <si>
+    <t>寵物對小孩特別緊張怎麼辦？</t>
+  </si>
+  <si>
+    <t>應逐步讓寵物接觸小孩，並教導小孩溫柔安靜地互動。可從短時間陪伴開始，當寵物保持冷靜時給予獎勵，逐步延長互動時間，建立正面經驗。</t>
+  </si>
+  <si>
+    <t>狗狗容易對其他狗吠叫，怎麼改善？</t>
+  </si>
+  <si>
+    <t>應先保持安全距離，當狗狗冷靜觀察時給予獎勵，逐步縮短距離。若出現吠叫，應立即轉移注意力，避免正面衝突。持續訓練能幫助降低過度反應。</t>
+  </si>
+  <si>
+    <t>貓咪能和其他人類建立感情嗎？</t>
+  </si>
+  <si>
+    <t>能，但需要時間。貓咪通常會對主要飼主最親近，但透過日常互動（餵食、遊戲、溫柔撫摸），其他家庭成員也能逐漸與牠建立信任與感情。</t>
+  </si>
+  <si>
+    <t>如何正確引入新寵物？</t>
+  </si>
+  <si>
+    <t>應採取漸進方式，先讓新寵物有獨立空間，再透過聞氣味、隔著門或柵欄見面，逐步增加接觸時間。直接讓陌生寵物面對面可能導致衝突與壓力。</t>
+  </si>
+  <si>
+    <t>兩隻狗相處常打架怎麼辦？</t>
+  </si>
+  <si>
+    <t>需觀察打架是玩耍還是爭奪資源。避免在有食物、玩具時讓牠們接觸，並建立清楚的規矩，例如先讓一隻坐下再給獎勵。若攻擊行為嚴重，建議找行為訓練師協助。</t>
+  </si>
+  <si>
+    <t>多隻貓咪怎麼避免爭地盤？</t>
+  </si>
+  <si>
+    <t>貓咪對領域敏感，多貓家庭應提供足夠的貓砂盆（至少 n+1 原則）、食盆與休息空間。可利用多層架、貓跳台增加垂直空間，減少競爭。</t>
+  </si>
+  <si>
+    <t>狗狗和貓咪可以和平共處嗎？</t>
+  </si>
+  <si>
+    <t>可以，但需要耐心。應先讓狗狗在牽繩下接觸，避免追逐；貓咪需要有高處或安全區域能撤退。逐步增加接觸時間，並在彼此冷靜時給予獎勵，建立正向關聯。</t>
+  </si>
+  <si>
+    <t>新寵物進家後舊寵物出現嫉妒怎麼辦？</t>
+  </si>
+  <si>
+    <t>要保持對舊寵物的關注，不要因新寵物到來而忽略。可在舊寵物面前給新寵物獎勵時，同時給舊寵物同等獎勵，避免比較心理。</t>
+  </si>
+  <si>
+    <t>如何避免食物引起的衝突？</t>
+  </si>
+  <si>
+    <t>應分開餵食，避免共同使用一個食盆。若需要同時餵食，應保持距離或用圍欄隔開，讓每隻寵物能安心進食，降低搶食與護食的風險。</t>
+  </si>
+  <si>
+    <t>小動物（兔子、倉鼠）能和狗貓相處嗎？</t>
+  </si>
+  <si>
+    <t>大多數情況下不建議直接混養，因為狗貓天生有狩獵本能，可能會追逐或攻擊小動物。如果要養，應分開飼養，僅在監督下讓牠們短暫接觸，並以安全籠具隔離。</t>
+  </si>
+  <si>
+    <t>多寵家庭如何分配注意力？</t>
+  </si>
+  <si>
+    <t>應確保每隻寵物都有單獨的陪伴時間，例如單獨散步或遊戲。避免偏心，並觀察個別需求（活潑的需要更多活動、膽小的需要更多安全感）。</t>
+  </si>
+  <si>
+    <t>如何判斷寵物是否能與其他動物和諧相處？</t>
+  </si>
+  <si>
+    <t>觀察其肢體語言：若能冷靜嗅聞、尾巴放鬆、耳朵自然，通常能適應；若出現咆哮、毛髮豎立或持續躲藏，表示仍需要更多時間與空間，不宜強迫。</t>
+  </si>
+  <si>
+    <t>多寵家庭出現嚴重衝突怎麼辦？</t>
+  </si>
+  <si>
+    <t>若打架頻繁且導致受傷，應立即分隔飼養，避免惡化。接下來可透過漸進式再社交訓練，或尋求專業行為治療師與獸醫的協助。部分情況下，可能需要長期分區生活。</t>
+  </si>
+  <si>
+    <t>狗狗每天需要睡多久？</t>
+  </si>
+  <si>
+    <t>成犬平均每天睡眠 12–14 小時，幼犬則需要 18–20 小時。大型犬的睡眠時間通常比小型犬更長。睡眠能幫助牠們恢復精力與維持健康。</t>
+  </si>
+  <si>
+    <t>貓咪每天需要睡多久？</t>
+  </si>
+  <si>
+    <t>貓咪平均每天睡眠 12–16 小時，有時甚至長達 20 小時。這是天性，因為貓科動物習慣短時間高強度活動後長時間休息。</t>
+  </si>
+  <si>
+    <t>寵物的睡眠需要固定時間嗎？</t>
+  </si>
+  <si>
+    <t>不需要完全固定，但規律的日常作息能幫助寵物更穩定，例如每天固定時間散步、進食與休息，讓牠們更容易進入安穩睡眠。</t>
+  </si>
+  <si>
+    <t>為什麼狗狗晚上會吠叫？</t>
+  </si>
+  <si>
+    <t>可能是因為聽到外界聲音、焦慮或需要排泄。應先確認基本需求是否滿足，並訓練牠在夜晚保持安靜。若頻繁吠叫，需檢查是否有焦慮或健康問題。</t>
+  </si>
+  <si>
+    <t>為什麼貓咪半夜特別活躍？</t>
+  </si>
+  <si>
+    <t>貓咪屬於晨昏活動型，容易在清晨與半夜活躍。若影響作息，可以在睡前與牠多進行互動遊戲消耗體力，並提供夜間可自行玩的玩具。</t>
+  </si>
+  <si>
+    <t>寵物需要有專屬睡覺的地方嗎？</t>
+  </si>
+  <si>
+    <t>需要。提供專屬的床墊或窩能讓牠們感到安全與舒適。位置應放在安靜無干擾的地方，避免過度吵雜或風吹直吹。</t>
+  </si>
+  <si>
+    <t>可以讓寵物跟主人一起睡嗎？</t>
+  </si>
+  <si>
+    <t>這取決於飼主與寵物習慣。一起睡能增進感情，但也可能造成過敏、衛生或睡眠中被打擾的問題。若選擇同睡，應確保寵物已驅蟲且定期清潔。</t>
+  </si>
+  <si>
+    <t>寵物睡覺時打呼正常嗎？</t>
+  </si>
+  <si>
+    <t>部分短鼻犬種（如法鬥、巴哥）因呼吸道構造會打呼，屬正常現象。但若出現呼吸困難、頻繁驚醒，可能是呼吸道疾病或肥胖引起，需就醫檢查。</t>
+  </si>
+  <si>
+    <t>狗狗白天睡很多，晚上卻不睡怎麼辦？</t>
+  </si>
+  <si>
+    <t>這可能是白天活動不足導致。應增加白天的散步與遊戲時間，讓牠消耗體力，自然在晚上更容易入睡。</t>
+  </si>
+  <si>
+    <t>寵物睡姿有什麼含義？</t>
+  </si>
+  <si>
+    <t>蜷縮睡表示尋求安全感；四腳朝天則代表放鬆與信任環境；趴睡多表示輕度休息，隨時準備起身。透過睡姿能大致判斷寵物當下的心理狀態。</t>
+  </si>
+  <si>
+    <t>幼犬幼貓晚上常常醒來怎麼辦？</t>
+  </si>
+  <si>
+    <t>幼年期睡眠尚未穩定，夜間醒來多半是因為飢餓或需要排泄。可在睡前餵食並帶去排泄，逐步訓練牠們學會整夜睡眠。</t>
+  </si>
+  <si>
+    <t>寵物睡覺會抽動或發出聲音是正常的嗎？</t>
+  </si>
+  <si>
+    <t>多數情況下是正常的快速動眼期（REM）夢境活動，寵物可能在夢中跑動或發出聲音。但若抽動過於劇烈，伴隨持續抽搐，可能是癲癇或神經疾病，需就醫檢查。</t>
+  </si>
+  <si>
+    <t>老年寵物為什麼睡得比年輕時更多？</t>
+  </si>
+  <si>
+    <t>老年寵物活動力下降，身體需要更多時間休息。通常每天可睡 16–20 小時。只要食慾、精神和如廁正常，多睡屬於自然老化現象。</t>
+  </si>
+  <si>
+    <t>老年寵物突然夜間吵鬧怎麼辦？</t>
+  </si>
+  <si>
+    <t>這可能是認知功能退化（寵物失智）的徵兆，例如日夜顛倒、迷路或焦躁。可透過規律作息、補充腦部保健品或在獸醫建議下使用藥物改善。</t>
+  </si>
+  <si>
+    <t>怎麼幫助焦慮的寵物入睡？</t>
+  </si>
+  <si>
+    <t>可透過安靜的環境、播放輕音樂、使用安撫玩具或擴香（如寵物專用費洛蒙）來減輕焦慮。規律的作息與睡前互動遊戲，也能讓牠更快放鬆。</t>
+  </si>
+  <si>
+    <t>寵物半夜吵鬧，應該制止還是忽視？</t>
+  </si>
+  <si>
+    <t>需先判斷原因。如果是需要排泄或健康問題，不應忽視；但若是因為想要關注而吵鬧，則不應立即回應，否則會強化行為。正確做法是建立白天充分活動與睡前固定作息。</t>
+  </si>
+  <si>
+    <t>寵物會夢遊嗎？</t>
+  </si>
+  <si>
+    <t>少見，但部分狗狗會在夢中走動或輕度夢遊。通常無害，但若伴隨頻繁發作或撞擊家具，應就醫排除癲癇或神經問題。</t>
+  </si>
+  <si>
+    <t>怎麼讓貓咪在晚上更安靜？</t>
+  </si>
+  <si>
+    <t>可在睡前進行「捕獵遊戲」讓牠耗盡精力，再給少量食物，模擬「狩獵—進食—休息」的自然循環。這能幫助貓咪夜間更安定。</t>
+  </si>
+  <si>
+    <t>寵物睡眠品質不佳會影響健康嗎？</t>
+  </si>
+  <si>
+    <t>會。長期睡眠不足可能導致免疫力下降、情緒焦躁，甚至加重慢性疾病。若寵物經常夜間吵鬧或無法入睡，應尋找原因並調整生活方式。</t>
+  </si>
+  <si>
+    <t>如何建立良好的寵物作息習慣？</t>
+  </si>
+  <si>
+    <t>飼主應固定餵食、運動與睡眠時間，避免隨意打擾寵物休息。透過規律的生活節奏，寵物會逐漸養成穩定的作息，自然睡眠品質也會提升。</t>
+  </si>
+  <si>
+    <t>如何避免寵物誤食危險物品？</t>
+  </si>
+  <si>
+    <t>應將清潔劑、藥物、巧克力、葡萄、洋蔥等有毒物放置於寵物無法觸及的位置。垃圾桶建議有蓋子，避免寵物翻找。若發現誤食，應立即送醫。</t>
+  </si>
+  <si>
+    <t>家裡有電線怎麼防止寵物咬？</t>
+  </si>
+  <si>
+    <t>可使用電線保護套、苦味噴劑，並提供合法的咬咬玩具轉移注意力。幼犬幼貓特別容易咬電線，環境必須加強防護。</t>
+  </si>
+  <si>
+    <t>廚房對寵物有哪些潛在危險？</t>
+  </si>
+  <si>
+    <t>熱鍋、刀具、食材（如洋蔥、大蒜）都可能造成危害。建議烹飪時不要讓寵物進入廚房，並保持食材及器具收納妥當。</t>
+  </si>
+  <si>
+    <t>如何避免寵物跌落陽台或窗戶？</t>
+  </si>
+  <si>
+    <t>必須加裝防護網或欄杆，尤其對貓咪來說，高處墜落非常危險。所謂的「高樓症候群」在都市中相當常見。</t>
+  </si>
+  <si>
+    <t>寵物與家中小孩玩耍會有危險嗎？</t>
+  </si>
+  <si>
+    <t>若未監督，可能造成小孩被抓傷或寵物被粗暴對待。應建立遊戲規範，並安排安全的互動方式，避免雙方受傷。</t>
+  </si>
+  <si>
+    <t>如何避免寵物被門夾到？</t>
+  </si>
+  <si>
+    <t>可安裝緩衝裝置或固定門片，避免突然關上。小型寵物經常因門縫意外受傷，飼主需特別注意。</t>
+  </si>
+  <si>
+    <t>家裡養多寵物時，怎麼預防打架？</t>
+  </si>
+  <si>
+    <t>應分開食盆、水盆與玩具，避免競爭。若出現衝突，應立即分隔空間，逐步再進行社交訓練。</t>
+  </si>
+  <si>
+    <t>如何防止寵物被家具夾住或卡住？</t>
+  </si>
+  <si>
+    <t>應封閉家具縫隙，避免小型犬貓或幼年寵物卡在沙發、床底。定期檢查環境，確保安全。</t>
+  </si>
+  <si>
+    <t>有毒植物對寵物有危害嗎？</t>
+  </si>
+  <si>
+    <t>有。百合、杜鵑、蘆薈、鈴蘭等常見植物對貓狗有毒，可能導致腎衰竭或心臟中毒。應避免擺放在家中或寵物可接觸的地方。</t>
+  </si>
+  <si>
+    <t>寵物單獨在家時如何確保安全？</t>
+  </si>
+  <si>
+    <t>避免留下危險物品，並限制活動範圍（如使用寵物圍欄）。同時可提供玩具與水，減少焦慮與無聊導致的破壞行為。</t>
+  </si>
+  <si>
+    <t>地震時應如何保護寵物？</t>
+  </si>
+  <si>
+    <t>應先確保自身安全，再將寵物放入運輸籠或用牽繩控制，避免驚嚇逃跑。準備緊急避難包，內含食物、水與寵物必需品。</t>
+  </si>
+  <si>
+    <t>火災發生時如何應對？</t>
+  </si>
+  <si>
+    <t>應迅速將寵物放入運輸籠帶離火場。若煙霧瀰漫，應保持低姿勢並用濕布保護寵物呼吸。平時要在家中張貼「有寵物」提示，方便消防員救援。</t>
+  </si>
+  <si>
+    <t>颱風或洪水來襲時該怎麼辦？</t>
+  </si>
+  <si>
+    <t>應事先規劃安全避難地點，確保寵物可一同進入。避難包應包含乾糧、水、藥物、毛毯與寵物證件，至少能維持 3–5 天。</t>
+  </si>
+  <si>
+    <t>寵物走失時第一步該做什麼？</t>
+  </si>
+  <si>
+    <t>立即搜尋周邊並呼喊牠的名字，接著通知當地收容所與獸醫院。若寵物有晶片與項圈名牌，找回機率將大幅提高。</t>
+  </si>
+  <si>
+    <t>寵物晶片的重要性是什麼？</t>
+  </si>
+  <si>
+    <t>晶片能提供永久身份辨識，走失時由收容單位或獸醫掃描即可找到飼主資訊。搭配名牌與 GPS 定位裝置效果更佳。</t>
+  </si>
+  <si>
+    <t>避難時寵物不能進入庇護所怎麼辦？</t>
+  </si>
+  <si>
+    <t>應事先查詢寵物友善的庇護所或安排替代方案（如親友家）。若必須分開，需留下食物、水與安全環境，但這僅是最後不得已的選擇。</t>
+  </si>
+  <si>
+    <t>颱風或大雨時，狗狗排泄怎麼辦？</t>
+  </si>
+  <si>
+    <t>可提前訓練狗狗在室內尿墊如廁。若必須外出，應使用雨衣、雨靴，並縮短時間，確保安全後立即返回。</t>
+  </si>
+  <si>
+    <t>寵物遇到驚嚇逃跑後回家了，要注意什麼？</t>
+  </si>
+  <si>
+    <t>應檢查有無外傷、中毒或骨折。即使外觀正常，也可能因驚嚇導致脫水或中暑，建議帶去獸醫檢查。</t>
+  </si>
+  <si>
+    <t>為寵物準備避難包需要哪些物品？</t>
+  </si>
+  <si>
+    <t>包含 3–5 天的乾糧與瓶裝水、藥物、健康證明、食盆、水碗、毛毯、玩具、排泄用品（貓砂或尿墊）、運輸籠與牽繩。</t>
+  </si>
+  <si>
+    <t>如何幫助寵物面對災後壓力？</t>
+  </si>
+  <si>
+    <t>災後寵物可能出現焦躁、吠叫或不吃飯。應給予熟悉的物品（毛毯、玩具）、固定的作息與安撫，並避免過度責罵。若長期異常，應諮詢獸醫或行為專家。</t>
+  </si>
+  <si>
+    <t>狗狗常見的慢性疾病有哪些？</t>
+  </si>
+  <si>
+    <t>最常見的包括關節炎、心臟病、腎臟病、糖尿病與皮膚過敏。這些疾病通常發展緩慢，需長期觀察與治療。</t>
+  </si>
+  <si>
+    <t>貓咪常見的慢性疾病有哪些？</t>
+  </si>
+  <si>
+    <t>以慢性腎臟病、甲狀腺機能亢進、糖尿病與泌尿道疾病最為常見，尤其在中老年貓咪身上比例更高。</t>
+  </si>
+  <si>
+    <t>如何發現狗狗可能有心臟病？</t>
+  </si>
+  <si>
+    <t>症狀包括咳嗽、容易疲倦、運動後喘、體重下降或腹部水腫。若狗狗在休息時也呼吸急促，需盡快帶去檢查。</t>
+  </si>
+  <si>
+    <t>貓咪腎臟病的早期徵兆是什麼？</t>
+  </si>
+  <si>
+    <t>會喝水量增加、尿量變多、體重減輕、食慾下降。定期驗血與驗尿能提早發現，因為早期往往不易被飼主察覺。</t>
+  </si>
+  <si>
+    <t>狗狗糖尿病有哪些症狀？</t>
+  </si>
+  <si>
+    <t>會出現喝水多、尿多、體重減輕但食慾旺盛。若未治療可能導致白內障、神經病變甚至酮酸中毒。</t>
+  </si>
+  <si>
+    <t>貓咪為什麼容易得甲狀腺機能亢進？</t>
+  </si>
+  <si>
+    <t>多見於老年貓，主要因為甲狀腺腫瘤或過度增生。症狀包括食量增加但體重下降、焦躁不安、心跳加快。</t>
+  </si>
+  <si>
+    <t>關節炎如何影響寵物？</t>
+  </si>
+  <si>
+    <t>患有關節炎的狗貓會活動力下降、上下樓梯困難、起身緩慢或跛行。治療上可使用關節保健品、止痛藥並控制體重。</t>
+  </si>
+  <si>
+    <t>寵物會得高血壓嗎？</t>
+  </si>
+  <si>
+    <t>會。高血壓常見於腎臟病、內分泌疾病或心臟病的寵物。若未控制，可能導致失明或中風。需透過藥物與飲食管理控制血壓。</t>
+  </si>
+  <si>
+    <t>貓咪泌尿道疾病的危險性？</t>
+  </si>
+  <si>
+    <t>特別是公貓，泌尿道阻塞會導致無法排尿，是緊急狀況，若未立即治療可能造成腎衰竭甚至死亡。</t>
+  </si>
+  <si>
+    <t>肥胖對寵物有什麼影響？</t>
+  </si>
+  <si>
+    <t>肥胖會增加糖尿病、關節炎、心臟病、呼吸問題與壽命縮短的風險。體重控制是最重要的預防方式。</t>
   </si>
 </sst>
 </file>
@@ -5892,6 +6316,618 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F35005D-CAFC-4BF7-9BF5-8DDB6F1C8458}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="55.125" customWidth="1"/>
+    <col min="2" max="2" width="124.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>679</v>
+      </c>
+      <c r="B2" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B3" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>683</v>
+      </c>
+      <c r="B4" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>685</v>
+      </c>
+      <c r="B5" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>431</v>
+      </c>
+      <c r="B6" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>688</v>
+      </c>
+      <c r="B7" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>690</v>
+      </c>
+      <c r="B8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>692</v>
+      </c>
+      <c r="B9" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>694</v>
+      </c>
+      <c r="B10" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>696</v>
+      </c>
+      <c r="B11" t="s">
+        <v>697</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E0741C3-8655-46D5-BDC8-D64C5900262F}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="68.375" customWidth="1"/>
+    <col min="2" max="2" width="95.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B2" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>700</v>
+      </c>
+      <c r="B3" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>702</v>
+      </c>
+      <c r="B4" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>704</v>
+      </c>
+      <c r="B5" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>706</v>
+      </c>
+      <c r="B6" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>708</v>
+      </c>
+      <c r="B7" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>710</v>
+      </c>
+      <c r="B8" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>712</v>
+      </c>
+      <c r="B9" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>714</v>
+      </c>
+      <c r="B10" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>716</v>
+      </c>
+      <c r="B11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1841643-5600-44B4-B680-726A023CB9DD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="68.875" customWidth="1"/>
+    <col min="2" max="2" width="94.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>718</v>
+      </c>
+      <c r="B2" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>720</v>
+      </c>
+      <c r="B3" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>722</v>
+      </c>
+      <c r="B4" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>724</v>
+      </c>
+      <c r="B5" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>726</v>
+      </c>
+      <c r="B6" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>728</v>
+      </c>
+      <c r="B7" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>730</v>
+      </c>
+      <c r="B8" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>732</v>
+      </c>
+      <c r="B9" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>734</v>
+      </c>
+      <c r="B10" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>736</v>
+      </c>
+      <c r="B11" t="s">
+        <v>737</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F08A0F1-4C33-4CAB-BDF7-E456CA948EDD}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="76.125" customWidth="1"/>
+    <col min="2" max="2" width="96.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B2" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>740</v>
+      </c>
+      <c r="B3" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B4" t="s">
+        <v>743</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>744</v>
+      </c>
+      <c r="B5" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>746</v>
+      </c>
+      <c r="B6" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>748</v>
+      </c>
+      <c r="B7" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>750</v>
+      </c>
+      <c r="B8" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>752</v>
+      </c>
+      <c r="B9" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>754</v>
+      </c>
+      <c r="B10" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>756</v>
+      </c>
+      <c r="B11" t="s">
+        <v>757</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44AE3091-41D5-46EA-9749-691504CF0EC5}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="69.875" customWidth="1"/>
+    <col min="2" max="2" width="95.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B2" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>760</v>
+      </c>
+      <c r="B3" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>762</v>
+      </c>
+      <c r="B4" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>764</v>
+      </c>
+      <c r="B5" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>766</v>
+      </c>
+      <c r="B6" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>768</v>
+      </c>
+      <c r="B7" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>770</v>
+      </c>
+      <c r="B8" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>772</v>
+      </c>
+      <c r="B9" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B10" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>776</v>
+      </c>
+      <c r="B11" t="s">
+        <v>777</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45E213FA-C52E-47ED-81A0-783069CBDCF3}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="72.25" customWidth="1"/>
+    <col min="2" max="2" width="100.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>778</v>
+      </c>
+      <c r="B2" t="s">
+        <v>779</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>780</v>
+      </c>
+      <c r="B3" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>782</v>
+      </c>
+      <c r="B4" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>784</v>
+      </c>
+      <c r="B5" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>786</v>
+      </c>
+      <c r="B6" t="s">
+        <v>787</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>788</v>
+      </c>
+      <c r="B7" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>790</v>
+      </c>
+      <c r="B8" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>792</v>
+      </c>
+      <c r="B9" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>794</v>
+      </c>
+      <c r="B10" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>796</v>
+      </c>
+      <c r="B11" t="s">
+        <v>797</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{532B40C6-DF30-4B29-B9D0-4F29D5AC34C2}">
   <dimension ref="A1:D10"/>
@@ -6039,6 +7075,108 @@
       </c>
       <c r="D10" t="s">
         <v>99</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32200461-A426-47ED-A4A2-84AFCCFFDE89}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="58.625" customWidth="1"/>
+    <col min="2" max="2" width="87.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>400</v>
+      </c>
+      <c r="B1" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>798</v>
+      </c>
+      <c r="B2" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>800</v>
+      </c>
+      <c r="B3" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>802</v>
+      </c>
+      <c r="B4" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>804</v>
+      </c>
+      <c r="B5" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>806</v>
+      </c>
+      <c r="B6" t="s">
+        <v>807</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>808</v>
+      </c>
+      <c r="B7" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>810</v>
+      </c>
+      <c r="B8" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>812</v>
+      </c>
+      <c r="B9" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>814</v>
+      </c>
+      <c r="B10" t="s">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>816</v>
+      </c>
+      <c r="B11" t="s">
+        <v>817</v>
       </c>
     </row>
   </sheetData>
